--- a/docs/testbook/ClinicaFlow_TestBook_API.xlsx
+++ b/docs/testbook/ClinicaFlow_TestBook_API.xlsx
@@ -5,22 +5,23 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\valen\clinicaflow\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\valen\clinicaflow\docs\testbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69DF5C9D-C4B7-4B24-BF8F-21EB9E3D10CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B829CA6-33F3-4444-B0F3-1115C5D9F990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{1C9960E8-B103-4EFA-9509-2FD0D5F86CF0}"/>
+    <workbookView xWindow="20370" yWindow="-4770" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1C9960E8-B103-4EFA-9509-2FD0D5F86CF0}"/>
   </bookViews>
   <sheets>
     <sheet name="ClinicaFlow_TestBook_API" sheetId="1" r:id="rId1"/>
+    <sheet name="TS1_20260321" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="159">
   <si>
     <t>ID Test</t>
   </si>
@@ -79,9 +80,6 @@
     <t>La specializzazione viene creata correttamente e viene restituito un id valorizzato.</t>
   </si>
   <si>
-    <t xml:space="preserve"> "TC01_CreateSpecialty_Success.png"</t>
-  </si>
-  <si>
     <t>TC02</t>
   </si>
   <si>
@@ -106,9 +104,6 @@
     <t>Il sistema rifiuta la creazione della specializzazione duplicata.</t>
   </si>
   <si>
-    <t xml:space="preserve"> "TC03_CreateDuplicateSpecialty_Conflict.png"</t>
-  </si>
-  <si>
     <t>TC04</t>
   </si>
   <si>
@@ -133,18 +128,6 @@
     <t>Verificare la creazione di un medico con specializzazione valida.</t>
   </si>
   <si>
-    <t>{"firstName":"Luca","lastName":"Bianchi","specialtyId":1}</t>
-  </si>
-  <si>
-    <t>Il medico viene creato correttamente ed Ã¨ associato a Cardiologia.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "TC05_CreateDoctor_Success.png"</t>
-  </si>
-  <si>
-    <t>Se gli ID nel database non partono da 1, usare l'id reale di Cardiologia.</t>
-  </si>
-  <si>
     <t>TC06</t>
   </si>
   <si>
@@ -157,12 +140,6 @@
     <t>400 Bad Request</t>
   </si>
   <si>
-    <t>Il sistema rifiuta la richiesta perchÃ© la specializzazione non esiste.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "TC06_CreateDoctor_InvalidSpecialty_BadRequest.png"</t>
-  </si>
-  <si>
     <t>TC07</t>
   </si>
   <si>
@@ -193,9 +170,6 @@
     <t>Lo slot viene creato correttamente con isAvailable = true.</t>
   </si>
   <si>
-    <t xml:space="preserve"> "TC08_CreateAvailabilitySlot_Success.png"</t>
-  </si>
-  <si>
     <t>Se l'id del medico non Ã¨ 1, sostituirlo con quello reale.</t>
   </si>
   <si>
@@ -208,12 +182,6 @@
     <t>{"doctorId":1,"startTime":"2026-03-22T09:15:00","endTime":"2026-03-22T09:45:00"}</t>
   </si>
   <si>
-    <t>Il sistema rifiuta lo slot perchÃ© si sovrappone a uno slot esistente dello stesso medico.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "TC09_CreateOverlappingSlot_Conflict.png"</t>
-  </si>
-  <si>
     <t>TC10</t>
   </si>
   <si>
@@ -229,9 +197,6 @@
     <t>L'appuntamento viene creato correttamente con stato Scheduled.</t>
   </si>
   <si>
-    <t xml:space="preserve"> "TC10_CreateAppointment_Success.png"</t>
-  </si>
-  <si>
     <t>Usare gli id reali di paziente e slot, se diversi.</t>
   </si>
   <si>
@@ -244,12 +209,6 @@
     <t>{"patientId":1,"availabilitySlotId":1,"notes":"Tentativo di seconda prenotazione"}</t>
   </si>
   <si>
-    <t>Il sistema rifiuta la richiesta perchÃ© lo slot non Ã¨ piÃ¹ disponibile.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "TC11_DoubleBooking_Conflict.png"</t>
-  </si>
-  <si>
     <t>TC12</t>
   </si>
   <si>
@@ -259,9 +218,6 @@
     <t>Lo slot restituito ha isAvailable = false.</t>
   </si>
   <si>
-    <t xml:space="preserve"> "TC12_GetAvailabilitySlot_NotAvailable.png"</t>
-  </si>
-  <si>
     <t>Sostituire l'id con quello reale dello slot.</t>
   </si>
   <si>
@@ -277,12 +233,6 @@
     <t>{"appointmentId":1,"diagnosis":"Ipertensione lieve","therapy":"Ridurre il consumo di sale e monitorare la pressione arteriosa","notes":"Controllo consigliato tra 30 giorni"}</t>
   </si>
   <si>
-    <t>Il sistema rifiuta la richiesta perchÃ© l'appuntamento non Ã¨ ancora completato.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "TC13_CreateMedicalReport_NotCompleted_BadRequest.png"</t>
-  </si>
-  <si>
     <t>TC14</t>
   </si>
   <si>
@@ -337,9 +287,6 @@
     <t>{"appointmentId":1,"diagnosis":"Test di duplicazione referto","therapy":"Non applicabile","notes":"Secondo referto non consentito"}</t>
   </si>
   <si>
-    <t>Il sistema rifiuta la creazione perchÃ© esiste giÃ  un referto per l'appuntamento indicato.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> "TC17_CreateDuplicateMedicalReport_Conflict.png"</t>
   </si>
   <si>
@@ -349,9 +296,6 @@
     <t>Verificare il recupero del referto associato a un appuntamento.</t>
   </si>
   <si>
-    <t>Il referto restituito Ã¨ correttamente associato all'appuntamento.</t>
-  </si>
-  <si>
     <t>TC19</t>
   </si>
   <si>
@@ -361,12 +305,6 @@
     <t>DELETE</t>
   </si>
   <si>
-    <t>Il sistema rifiuta l'eliminazione perchÃ© la specializzazione Ã¨ associata a uno o piÃ¹ medici.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> "TC19_DeleteSpecialty_WithDoctor_Conflict.png"</t>
-  </si>
-  <si>
     <t>TC20</t>
   </si>
   <si>
@@ -415,9 +353,6 @@
     <t>Lo slot restituito ha isAvailable = true.</t>
   </si>
   <si>
-    <t xml:space="preserve"> "TC23_GetAvailabilitySlot_Reopened_Success.png"</t>
-  </si>
-  <si>
     <t>/api/specialties</t>
   </si>
   <si>
@@ -455,6 +390,114 @@
   </si>
   <si>
     <t>/api/appointments/1/status</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>Specializzazione creata correttamente.</t>
+  </si>
+  <si>
+    <t>Esiste già una specializzazione con lo stesso nome.</t>
+  </si>
+  <si>
+    <t>L'elenco è completo</t>
+  </si>
+  <si>
+    <t>Il medico viene creato correttamente ed è associato a Cardiologia.</t>
+  </si>
+  <si>
+    <t>Il sistema rifiuta la richiesta perchè la specializzazione non esiste.</t>
+  </si>
+  <si>
+    <t>Il sistema rifiuta lo slot perchè si sovrappone a uno slot esistente dello stesso medico.</t>
+  </si>
+  <si>
+    <t>{"firstName":"Luca","lastName":"Bianchi","specialtyId":2}</t>
+  </si>
+  <si>
+    <t>Gli ID nel database non partono da 1 per test preliminare eseguito prima di questa sessione di test</t>
+  </si>
+  <si>
+    <t>La specializzazione indicata non esiste.</t>
+  </si>
+  <si>
+    <t>Medico creato correttamente</t>
+  </si>
+  <si>
+    <t>KO</t>
+  </si>
+  <si>
+    <t>Microsoft.Data.SqlClient.SqlException : Cannot insert the value NULL into column 'TaxCode', table 'ClinicaFlowDb.dbo.Patients'; column does not allow nulls. INSERT fails.</t>
+  </si>
+  <si>
+    <t>TC07_CreatePatient_bug01.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> TC06_CreateDoctor_InvalidSpecialty_BadRequest.png</t>
+  </si>
+  <si>
+    <t>TC01_CreateSpecialty_Success.png</t>
+  </si>
+  <si>
+    <t>TC03_CreateDuplicateSpecialty_Conflict.png</t>
+  </si>
+  <si>
+    <t>TC05_CreateDoctor_Success.png</t>
+  </si>
+  <si>
+    <t>TC08_CreateAvailabilitySlot_Success.png</t>
+  </si>
+  <si>
+    <t>TC09_CreateOverlappingSlot_Conflict.png</t>
+  </si>
+  <si>
+    <t>TC10_CreateAppointment_Success.png</t>
+  </si>
+  <si>
+    <t>TC11_DoubleBooking_Conflict.png</t>
+  </si>
+  <si>
+    <t>TC12_GetAvailabilitySlot_NotAvailable.png</t>
+  </si>
+  <si>
+    <t>TC13_CreateMedicalReport_NotCompleted_BadRequest.png</t>
+  </si>
+  <si>
+    <t>TC19_DeleteSpecialty_WithDoctor_Conflict.png</t>
+  </si>
+  <si>
+    <t>TC23_GetAvailabilitySlot_Reopened_Success.png</t>
+  </si>
+  <si>
+    <t>BUG01</t>
+  </si>
+  <si>
+    <t>Slot creato correttamente</t>
+  </si>
+  <si>
+    <t>Esiste già uno slot sovrapposto per il medico indicato.</t>
+  </si>
+  <si>
+    <t>Il sistema rifiuta la richiesta perchè l'appuntamento non è ancora completato.</t>
+  </si>
+  <si>
+    <t>Il sistema rifiuta la richiesta perchè lo slot non è più disponibile.</t>
+  </si>
+  <si>
+    <t>L'appuntamento indicato non esiste.</t>
+  </si>
+  <si>
+    <t>Il sistema rifiuta la creazione perchè esiste già un referto per l'appuntamento indicato.</t>
+  </si>
+  <si>
+    <t>Il referto restituito è correttamente associato all'appuntamento.</t>
+  </si>
+  <si>
+    <t>Il sistema rifiuta l'eliminazione perchè la specializzazione è associata a uno o più medici.</t>
+  </si>
+  <si>
+    <t>Non è possibile eliminare una specializzazione associata a uno o più medici.</t>
   </si>
 </sst>
 </file>
@@ -938,8 +981,17 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -985,7 +1037,232 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="48">
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -999,21 +1276,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}" name="Table1" displayName="Table1" ref="A1:L24" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}" name="Table1" displayName="Table1" ref="A1:L24" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{3860FCCE-8AB2-4BA5-A927-55A78AF301A2}" name="ID Test"/>
-    <tableColumn id="2" xr3:uid="{6B8298D4-C558-435B-BC50-DF9FF417402B}" name="Area"/>
-    <tableColumn id="3" xr3:uid="{53DE22B4-8437-4EA6-813E-2F0CF7E72133}" name="Obiettivo"/>
-    <tableColumn id="4" xr3:uid="{59024008-94B6-47E6-8C7F-69725DFAE6EC}" name="Endpoint"/>
-    <tableColumn id="5" xr3:uid="{DC8ACE73-D608-4E52-81FB-F85282B31F51}" name="Metodo HTTP"/>
-    <tableColumn id="6" xr3:uid="{E583E0AB-6285-4FCA-BC35-0CD0BFB6F457}" name="Payload JSON"/>
-    <tableColumn id="7" xr3:uid="{5BDBA1B2-61ED-47D6-88D1-CDE3D8CC9212}" name="Risultato atteso - Status Code"/>
-    <tableColumn id="8" xr3:uid="{F14E32B9-432F-43ED-9E31-411BF4ADBC3F}" name="Risultato atteso - Dettaglio"/>
-    <tableColumn id="9" xr3:uid="{DFDF46B3-7AFF-4643-9EAB-E56F926CE154}" name="Esito"/>
-    <tableColumn id="10" xr3:uid="{5192CEE0-B98B-4E21-8BEA-8F62C2DAC458}" name="Risultato ottenuto"/>
-    <tableColumn id="11" xr3:uid="{E9C64C9D-7B98-4D7D-8A82-64CB9D831A1C}" name="Screenshot"/>
-    <tableColumn id="12" xr3:uid="{D98AF63F-322C-4828-B53E-197F74FEE6FE}" name="Note"/>
+    <tableColumn id="1" xr3:uid="{3860FCCE-8AB2-4BA5-A927-55A78AF301A2}" name="ID Test" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{6B8298D4-C558-435B-BC50-DF9FF417402B}" name="Area" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{53DE22B4-8437-4EA6-813E-2F0CF7E72133}" name="Obiettivo" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{59024008-94B6-47E6-8C7F-69725DFAE6EC}" name="Endpoint" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{DC8ACE73-D608-4E52-81FB-F85282B31F51}" name="Metodo HTTP" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{E583E0AB-6285-4FCA-BC35-0CD0BFB6F457}" name="Payload JSON" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{5BDBA1B2-61ED-47D6-88D1-CDE3D8CC9212}" name="Risultato atteso - Status Code" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{F14E32B9-432F-43ED-9E31-411BF4ADBC3F}" name="Risultato atteso - Dettaglio" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{DFDF46B3-7AFF-4643-9EAB-E56F926CE154}" name="Esito" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{5192CEE0-B98B-4E21-8BEA-8F62C2DAC458}" name="Risultato ottenuto" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{E9C64C9D-7B98-4D7D-8A82-64CB9D831A1C}" name="Screenshot" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{D98AF63F-322C-4828-B53E-197F74FEE6FE}" name="Note" dataDxfId="16"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5EC5406F-ABEC-4C5A-BB6C-648C616B89A5}" name="Table13" displayName="Table13" ref="A1:L24" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{5009D189-63E8-4852-A288-87D6EC1E7033}" name="ID Test" dataDxfId="13"/>
+    <tableColumn id="2" xr3:uid="{84642470-32B1-46DB-88F2-1BC4AE8F75C8}" name="Area" dataDxfId="12"/>
+    <tableColumn id="3" xr3:uid="{4F14914F-A3C4-4267-A392-EC2D02D6ADDF}" name="Obiettivo" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{62A87606-C1B8-47E6-9530-D288374DCDF3}" name="Endpoint" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{19E09EE6-EB67-45CF-9A03-E0F0523DB6A0}" name="Metodo HTTP" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{A7AC84FA-A2F1-4930-BDDD-E380EE204368}" name="Payload JSON" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{25C18B10-E594-4E87-AD84-2A557086D8F7}" name="Risultato atteso - Status Code" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{94B79096-6200-43FE-8F50-1C48EB575740}" name="Risultato atteso - Dettaglio" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{AD4E1447-793D-4E65-9313-6A19D961F6AE}" name="Esito" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{B18252F9-BB1D-47B7-8E2C-F42387EC3664}" name="Risultato ottenuto" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{15A8AB07-0563-4A1C-839B-92039F98E2D5}" name="Screenshot" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{4BA21C77-65A7-407A-A5E1-0AA6154386E8}" name="Note" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1319,711 +1617,1576 @@
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="40.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="157.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29" customWidth="1"/>
-    <col min="8" max="8" width="85" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.42578125" customWidth="1"/>
-    <col min="10" max="10" width="19.28515625" customWidth="1"/>
-    <col min="11" max="11" width="58.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="64" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="29" style="2" customWidth="1"/>
+    <col min="8" max="8" width="41.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="41.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="58.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="64" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="2" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I10">
+    <cfRule type="cellIs" dxfId="47" priority="10" operator="equal">
+      <formula>"KO"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="46" priority="9" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:I19">
+    <cfRule type="cellIs" dxfId="44" priority="7" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="45" priority="8" operator="equal">
+      <formula>"KO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I20">
+    <cfRule type="cellIs" dxfId="42" priority="5" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="43" priority="6" operator="equal">
+      <formula>"KO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I21">
+    <cfRule type="cellIs" dxfId="40" priority="3" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="41" priority="4" operator="equal">
+      <formula>"KO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I24">
+    <cfRule type="cellIs" dxfId="39" priority="1" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="38" priority="2" operator="equal">
+      <formula>"KO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I24" xr:uid="{1E5ABA8E-0832-445D-8BB0-BB6759FFFC93}">
+      <formula1>"OK,KO"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FD9EF9F-CB0B-4D0D-A402-0DE892E54EC1}">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="29" style="2" customWidth="1"/>
+    <col min="8" max="8" width="41.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="41.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="58.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="64" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="E2" t="s">
+      <c r="K7" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="F8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="H8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="F21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="H3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="H21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>27</v>
-      </c>
-      <c r="K4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="F22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="G24" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D5" t="s">
-        <v>132</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" t="s">
-        <v>133</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" t="s">
-        <v>17</v>
-      </c>
-      <c r="H6" t="s">
-        <v>38</v>
-      </c>
-      <c r="K6" t="s">
-        <v>39</v>
-      </c>
-      <c r="L6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" t="s">
-        <v>133</v>
-      </c>
-      <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H7" t="s">
-        <v>45</v>
-      </c>
-      <c r="K7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" t="s">
-        <v>134</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" t="s">
-        <v>54</v>
-      </c>
-      <c r="D9" t="s">
-        <v>135</v>
-      </c>
-      <c r="E9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-      <c r="G9" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" t="s">
-        <v>56</v>
-      </c>
-      <c r="K9" t="s">
-        <v>57</v>
-      </c>
-      <c r="L9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" t="s">
-        <v>135</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" t="s">
-        <v>62</v>
-      </c>
-      <c r="K10" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="H24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="L24" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="C11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D11" t="s">
-        <v>136</v>
-      </c>
-      <c r="E11" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H11" t="s">
-        <v>68</v>
-      </c>
-      <c r="K11" t="s">
-        <v>69</v>
-      </c>
-      <c r="L11" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>71</v>
-      </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" t="s">
-        <v>136</v>
-      </c>
-      <c r="E12" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" t="s">
-        <v>73</v>
-      </c>
-      <c r="G12" t="s">
-        <v>26</v>
-      </c>
-      <c r="H12" t="s">
-        <v>74</v>
-      </c>
-      <c r="K12" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" t="s">
-        <v>137</v>
-      </c>
-      <c r="E13" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" t="s">
-        <v>78</v>
-      </c>
-      <c r="K13" t="s">
-        <v>79</v>
-      </c>
-      <c r="L13" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" t="s">
-        <v>138</v>
-      </c>
-      <c r="E14" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" t="s">
-        <v>84</v>
-      </c>
-      <c r="G14" t="s">
-        <v>44</v>
-      </c>
-      <c r="H14" t="s">
-        <v>85</v>
-      </c>
-      <c r="K14" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>87</v>
-      </c>
-      <c r="B15" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" t="s">
-        <v>144</v>
-      </c>
-      <c r="E15" t="s">
-        <v>89</v>
-      </c>
-      <c r="F15" t="s">
-        <v>90</v>
-      </c>
-      <c r="G15" t="s">
-        <v>91</v>
-      </c>
-      <c r="H15" t="s">
-        <v>92</v>
-      </c>
-      <c r="L15" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>94</v>
-      </c>
-      <c r="B16" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" t="s">
-        <v>139</v>
-      </c>
-      <c r="E16" t="s">
-        <v>31</v>
-      </c>
-      <c r="G16" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" t="s">
-        <v>96</v>
-      </c>
-      <c r="K16" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>98</v>
-      </c>
-      <c r="B17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" t="s">
-        <v>138</v>
-      </c>
-      <c r="E17" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" t="s">
-        <v>84</v>
-      </c>
-      <c r="G17" t="s">
-        <v>17</v>
-      </c>
-      <c r="H17" t="s">
-        <v>100</v>
-      </c>
-      <c r="K17" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" t="s">
-        <v>138</v>
-      </c>
-      <c r="E18" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" t="s">
-        <v>26</v>
-      </c>
-      <c r="H18" t="s">
-        <v>105</v>
-      </c>
-      <c r="K18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" t="s">
-        <v>82</v>
-      </c>
-      <c r="C19" t="s">
-        <v>108</v>
-      </c>
-      <c r="D19" t="s">
-        <v>140</v>
-      </c>
-      <c r="E19" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" t="s">
-        <v>32</v>
-      </c>
-      <c r="H19" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>110</v>
-      </c>
-      <c r="B20" t="s">
-        <v>13</v>
-      </c>
-      <c r="C20" t="s">
-        <v>111</v>
-      </c>
-      <c r="D20" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" t="s">
-        <v>112</v>
-      </c>
-      <c r="G20" t="s">
-        <v>26</v>
-      </c>
-      <c r="H20" t="s">
-        <v>113</v>
-      </c>
-      <c r="K20" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>115</v>
-      </c>
-      <c r="B21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D21" t="s">
-        <v>135</v>
-      </c>
-      <c r="E21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" t="s">
-        <v>117</v>
-      </c>
-      <c r="G21" t="s">
-        <v>17</v>
-      </c>
-      <c r="H21" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>119</v>
-      </c>
-      <c r="B22" t="s">
-        <v>65</v>
-      </c>
-      <c r="C22" t="s">
-        <v>120</v>
-      </c>
-      <c r="D22" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22" t="s">
-        <v>15</v>
-      </c>
-      <c r="F22" t="s">
-        <v>121</v>
-      </c>
-      <c r="G22" t="s">
-        <v>17</v>
-      </c>
-      <c r="H22" t="s">
-        <v>122</v>
-      </c>
-      <c r="L22" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>124</v>
-      </c>
-      <c r="B23" t="s">
-        <v>65</v>
-      </c>
-      <c r="C23" t="s">
-        <v>125</v>
-      </c>
-      <c r="D23" t="s">
-        <v>142</v>
-      </c>
-      <c r="E23" t="s">
-        <v>89</v>
-      </c>
-      <c r="F23" t="s">
-        <v>126</v>
-      </c>
-      <c r="G23" t="s">
-        <v>91</v>
-      </c>
-      <c r="H23" t="s">
-        <v>127</v>
-      </c>
-      <c r="L23" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>128</v>
-      </c>
-      <c r="B24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" t="s">
-        <v>129</v>
-      </c>
-      <c r="D24" t="s">
-        <v>143</v>
-      </c>
-      <c r="E24" t="s">
-        <v>31</v>
-      </c>
-      <c r="G24" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" t="s">
-        <v>130</v>
-      </c>
-      <c r="K24" t="s">
-        <v>131</v>
-      </c>
-      <c r="L24" t="s">
-        <v>80</v>
-      </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="I2:I10">
+    <cfRule type="cellIs" dxfId="36" priority="9" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="37" priority="10" operator="equal">
+      <formula>"KO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:I19">
+    <cfRule type="cellIs" dxfId="35" priority="7" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="34" priority="8" operator="equal">
+      <formula>"KO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I20">
+    <cfRule type="cellIs" dxfId="33" priority="5" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="6" operator="equal">
+      <formula>"KO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I21">
+    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="4" operator="equal">
+      <formula>"KO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I22:I24">
+    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+      <formula>"KO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I24" xr:uid="{8573BCBE-85B2-4D75-9CCE-728BBC8A9ED4}">
+      <formula1>"OK,KO"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
--- a/docs/testbook/ClinicaFlow_TestBook_API.xlsx
+++ b/docs/testbook/ClinicaFlow_TestBook_API.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\valen\clinicaflow\docs\testbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B829CA6-33F3-4444-B0F3-1115C5D9F990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B8CB74-FAEE-4705-BC84-56E602C9B112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-4770" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1C9960E8-B103-4EFA-9509-2FD0D5F86CF0}"/>
   </bookViews>
   <sheets>
     <sheet name="ClinicaFlow_TestBook_API" sheetId="1" r:id="rId1"/>
-    <sheet name="TS1_20260321" sheetId="2" r:id="rId2"/>
+    <sheet name="BUG" sheetId="3" r:id="rId2"/>
+    <sheet name="TS1_20260321" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="166">
   <si>
     <t>ID Test</t>
   </si>
@@ -498,6 +499,27 @@
   </si>
   <si>
     <t>Non è possibile eliminare una specializzazione associata a uno o più medici.</t>
+  </si>
+  <si>
+    <t>ID Bug</t>
+  </si>
+  <si>
+    <t>Errore</t>
+  </si>
+  <si>
+    <t>Priorità</t>
+  </si>
+  <si>
+    <t>ALTA</t>
+  </si>
+  <si>
+    <t>TS1_20260321</t>
+  </si>
+  <si>
+    <t>Sessione OK</t>
+  </si>
+  <si>
+    <t>Sessione KO</t>
   </si>
 </sst>
 </file>
@@ -640,7 +662,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -820,8 +842,20 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor theme="4" tint="0.59999389629810485"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="10">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -936,6 +970,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right style="thin">
+        <color theme="0"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -981,7 +1078,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -991,6 +1088,33 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1037,91 +1161,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="48">
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
+  <dxfs count="38">
     <dxf>
       <fill>
         <patternFill>
@@ -1146,7 +1186,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1167,21 +1214,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
+          <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1200,67 +1233,88 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1276,42 +1330,42 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}" name="Table1" displayName="Table1" ref="A1:L24" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}" name="Table1" displayName="Table1" ref="A1:L24" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{3860FCCE-8AB2-4BA5-A927-55A78AF301A2}" name="ID Test" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{6B8298D4-C558-435B-BC50-DF9FF417402B}" name="Area" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{53DE22B4-8437-4EA6-813E-2F0CF7E72133}" name="Obiettivo" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{59024008-94B6-47E6-8C7F-69725DFAE6EC}" name="Endpoint" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{DC8ACE73-D608-4E52-81FB-F85282B31F51}" name="Metodo HTTP" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{E583E0AB-6285-4FCA-BC35-0CD0BFB6F457}" name="Payload JSON" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{5BDBA1B2-61ED-47D6-88D1-CDE3D8CC9212}" name="Risultato atteso - Status Code" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{F14E32B9-432F-43ED-9E31-411BF4ADBC3F}" name="Risultato atteso - Dettaglio" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{DFDF46B3-7AFF-4643-9EAB-E56F926CE154}" name="Esito" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{5192CEE0-B98B-4E21-8BEA-8F62C2DAC458}" name="Risultato ottenuto" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{E9C64C9D-7B98-4D7D-8A82-64CB9D831A1C}" name="Screenshot" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{D98AF63F-322C-4828-B53E-197F74FEE6FE}" name="Note" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{3860FCCE-8AB2-4BA5-A927-55A78AF301A2}" name="ID Test" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{6B8298D4-C558-435B-BC50-DF9FF417402B}" name="Area" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{53DE22B4-8437-4EA6-813E-2F0CF7E72133}" name="Obiettivo" dataDxfId="33"/>
+    <tableColumn id="4" xr3:uid="{59024008-94B6-47E6-8C7F-69725DFAE6EC}" name="Endpoint" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{DC8ACE73-D608-4E52-81FB-F85282B31F51}" name="Metodo HTTP" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{E583E0AB-6285-4FCA-BC35-0CD0BFB6F457}" name="Payload JSON" dataDxfId="30"/>
+    <tableColumn id="7" xr3:uid="{5BDBA1B2-61ED-47D6-88D1-CDE3D8CC9212}" name="Risultato atteso - Status Code" dataDxfId="29"/>
+    <tableColumn id="8" xr3:uid="{F14E32B9-432F-43ED-9E31-411BF4ADBC3F}" name="Risultato atteso - Dettaglio" dataDxfId="28"/>
+    <tableColumn id="9" xr3:uid="{DFDF46B3-7AFF-4643-9EAB-E56F926CE154}" name="Esito" dataDxfId="27"/>
+    <tableColumn id="10" xr3:uid="{5192CEE0-B98B-4E21-8BEA-8F62C2DAC458}" name="Risultato ottenuto" dataDxfId="26"/>
+    <tableColumn id="11" xr3:uid="{E9C64C9D-7B98-4D7D-8A82-64CB9D831A1C}" name="Screenshot" dataDxfId="25"/>
+    <tableColumn id="12" xr3:uid="{D98AF63F-322C-4828-B53E-197F74FEE6FE}" name="Note" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5EC5406F-ABEC-4C5A-BB6C-648C616B89A5}" name="Table13" displayName="Table13" ref="A1:L24" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5EC5406F-ABEC-4C5A-BB6C-648C616B89A5}" name="Table13" displayName="Table13" ref="A1:L24" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{5009D189-63E8-4852-A288-87D6EC1E7033}" name="ID Test" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{84642470-32B1-46DB-88F2-1BC4AE8F75C8}" name="Area" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{4F14914F-A3C4-4267-A392-EC2D02D6ADDF}" name="Obiettivo" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{62A87606-C1B8-47E6-9530-D288374DCDF3}" name="Endpoint" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{19E09EE6-EB67-45CF-9A03-E0F0523DB6A0}" name="Metodo HTTP" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{A7AC84FA-A2F1-4930-BDDD-E380EE204368}" name="Payload JSON" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{25C18B10-E594-4E87-AD84-2A557086D8F7}" name="Risultato atteso - Status Code" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{94B79096-6200-43FE-8F50-1C48EB575740}" name="Risultato atteso - Dettaglio" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{AD4E1447-793D-4E65-9313-6A19D961F6AE}" name="Esito" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{B18252F9-BB1D-47B7-8E2C-F42387EC3664}" name="Risultato ottenuto" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{15A8AB07-0563-4A1C-839B-92039F98E2D5}" name="Screenshot" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{4BA21C77-65A7-407A-A5E1-0AA6154386E8}" name="Note" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{5009D189-63E8-4852-A288-87D6EC1E7033}" name="ID Test" dataDxfId="21"/>
+    <tableColumn id="2" xr3:uid="{84642470-32B1-46DB-88F2-1BC4AE8F75C8}" name="Area" dataDxfId="20"/>
+    <tableColumn id="3" xr3:uid="{4F14914F-A3C4-4267-A392-EC2D02D6ADDF}" name="Obiettivo" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{62A87606-C1B8-47E6-9530-D288374DCDF3}" name="Endpoint" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{19E09EE6-EB67-45CF-9A03-E0F0523DB6A0}" name="Metodo HTTP" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{A7AC84FA-A2F1-4930-BDDD-E380EE204368}" name="Payload JSON" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{25C18B10-E594-4E87-AD84-2A557086D8F7}" name="Risultato atteso - Status Code" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{94B79096-6200-43FE-8F50-1C48EB575740}" name="Risultato atteso - Dettaglio" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{AD4E1447-793D-4E65-9313-6A19D961F6AE}" name="Esito" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{B18252F9-BB1D-47B7-8E2C-F42387EC3664}" name="Risultato ottenuto" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{15A8AB07-0563-4A1C-839B-92039F98E2D5}" name="Screenshot" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{4BA21C77-65A7-407A-A5E1-0AA6154386E8}" name="Note" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2299,43 +2353,11 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:I10">
-    <cfRule type="cellIs" dxfId="47" priority="10" operator="equal">
-      <formula>"KO"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="46" priority="9" operator="equal">
+  <conditionalFormatting sqref="I2:I24">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I19">
-    <cfRule type="cellIs" dxfId="44" priority="7" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="45" priority="8" operator="equal">
-      <formula>"KO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I20">
-    <cfRule type="cellIs" dxfId="42" priority="5" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="43" priority="6" operator="equal">
-      <formula>"KO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="40" priority="3" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="41" priority="4" operator="equal">
-      <formula>"KO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I24">
-    <cfRule type="cellIs" dxfId="39" priority="1" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="38" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2353,6 +2375,107 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27CCBE7D-F26A-41C6-96A8-43D2BF97BCE3}">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr defaultColWidth="91.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="68.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="89.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="30.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"BASSA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"MEDIA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"ALTA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{78C482C4-A569-4755-A44B-F5FA399B9D9D}">
+      <formula1>"ALTA,MEDIA,BASSA"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FD9EF9F-CB0B-4D0D-A402-0DE892E54EC1}">
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2365,7 +2488,7 @@
     <col min="6" max="6" width="54.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="29" style="2" customWidth="1"/>
     <col min="8" max="8" width="41.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="7.42578125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" style="4" customWidth="1"/>
     <col min="10" max="10" width="41.7109375" style="1" customWidth="1"/>
     <col min="11" max="11" width="58.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="64" style="1" bestFit="1" customWidth="1"/>
@@ -2397,7 +2520,7 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -2435,7 +2558,7 @@
       <c r="H2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="4" t="s">
         <v>123</v>
       </c>
       <c r="J2" s="1" t="s">
@@ -2470,7 +2593,7 @@
       <c r="H3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="4" t="s">
         <v>123</v>
       </c>
       <c r="J3" s="1" t="s">
@@ -2502,7 +2625,7 @@
       <c r="H4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>123</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -2534,7 +2657,7 @@
       <c r="H5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>123</v>
       </c>
       <c r="J5" s="1" t="s">
@@ -2566,7 +2689,7 @@
       <c r="H6" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="4" t="s">
         <v>123</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -2604,7 +2727,7 @@
       <c r="H7" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="4" t="s">
         <v>123</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -2639,7 +2762,7 @@
       <c r="H8" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="4" t="s">
         <v>134</v>
       </c>
       <c r="J8" s="1" t="s">
@@ -2677,7 +2800,7 @@
       <c r="H9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="4" t="s">
         <v>123</v>
       </c>
       <c r="J9" s="1" t="s">
@@ -2715,7 +2838,7 @@
       <c r="H10" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="4" t="s">
         <v>123</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -2840,7 +2963,7 @@
       <c r="H14" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="4" t="s">
         <v>123</v>
       </c>
       <c r="J14" s="1" t="s">
@@ -3008,7 +3131,7 @@
       <c r="H20" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="I20" s="3" t="s">
+      <c r="I20" s="4" t="s">
         <v>123</v>
       </c>
       <c r="J20" s="1" t="s">
@@ -3043,7 +3166,7 @@
       <c r="H21" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="I21" s="4" t="s">
         <v>123</v>
       </c>
       <c r="J21" s="1" t="s">
@@ -3138,43 +3261,11 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="I2:I10">
-    <cfRule type="cellIs" dxfId="36" priority="9" operator="equal">
+  <conditionalFormatting sqref="I2:I24">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="10" operator="equal">
-      <formula>"KO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I19">
-    <cfRule type="cellIs" dxfId="35" priority="7" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="8" operator="equal">
-      <formula>"KO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I20">
-    <cfRule type="cellIs" dxfId="33" priority="5" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="6" operator="equal">
-      <formula>"KO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I21">
-    <cfRule type="cellIs" dxfId="31" priority="3" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="4" operator="equal">
-      <formula>"KO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I22:I24">
-    <cfRule type="cellIs" dxfId="29" priority="1" operator="equal">
-      <formula>"OK"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="28" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/testbook/ClinicaFlow_TestBook_API.xlsx
+++ b/docs/testbook/ClinicaFlow_TestBook_API.xlsx
@@ -8,21 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\valen\clinicaflow\docs\testbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B8CB74-FAEE-4705-BC84-56E602C9B112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99819984-289C-4DA6-AE98-9D390E4B0077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-4770" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1C9960E8-B103-4EFA-9509-2FD0D5F86CF0}"/>
+    <workbookView xWindow="20370" yWindow="-4770" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{1C9960E8-B103-4EFA-9509-2FD0D5F86CF0}"/>
   </bookViews>
   <sheets>
     <sheet name="ClinicaFlow_TestBook_API" sheetId="1" r:id="rId1"/>
     <sheet name="BUG" sheetId="3" r:id="rId2"/>
     <sheet name="TS1_20260321" sheetId="2" r:id="rId3"/>
+    <sheet name="TS2_20260321" sheetId="4" r:id="rId4"/>
+    <sheet name="TS3_20260321" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="174">
   <si>
     <t>ID Test</t>
   </si>
@@ -520,6 +522,44 @@
   </si>
   <si>
     <t>Sessione KO</t>
+  </si>
+  <si>
+    <t>{
+  "firstName": "Mario",
+  "lastName": "Rossi",
+  "taxCode": "RSSMRA85D12H501X",
+  "dateOfBirth": "1985-04-12T00:00:00",
+  "phone": "3331234567",
+  "email": "mario.rossi@example.com"
+}</t>
+  </si>
+  <si>
+    <t>Microsoft.Data.SqlClient.SqlException : Invalid column name 'DateOfBirth'.</t>
+  </si>
+  <si>
+    <t>TC07_CreatePatient_bug02.png</t>
+  </si>
+  <si>
+    <t>BUG02</t>
+  </si>
+  <si>
+    <t>TS2_20260321</t>
+  </si>
+  <si>
+    <t>{
+  "firstName": "Mario",
+  "lastName": "Rossi",
+  "taxCode": "RSSMRA85D12H501X",
+  "birthDate": "1985-04-12T00:00:00",
+  "phone": "3331234567",
+  "email": "mario.rossi@example.com"
+}</t>
+  </si>
+  <si>
+    <t>Paziente creato correttamente con ID:3</t>
+  </si>
+  <si>
+    <t>TC07_CreatePatient_Success.png</t>
   </si>
 </sst>
 </file>
@@ -1078,7 +1118,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1098,13 +1138,13 @@
     <xf numFmtId="0" fontId="13" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1113,8 +1153,11 @@
     <xf numFmtId="0" fontId="13" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1161,7 +1204,49 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="38">
+  <dxfs count="67">
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1177,6 +1262,48 @@
       </fill>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
@@ -1186,6 +1313,34 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FFFFC000"/>
         </patternFill>
       </fill>
@@ -1212,40 +1367,19 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1330,42 +1464,84 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}" name="Table1" displayName="Table1" ref="A1:L24" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}" name="Table1" displayName="Table1" ref="A1:L24" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{3860FCCE-8AB2-4BA5-A927-55A78AF301A2}" name="ID Test" dataDxfId="35"/>
-    <tableColumn id="2" xr3:uid="{6B8298D4-C558-435B-BC50-DF9FF417402B}" name="Area" dataDxfId="34"/>
-    <tableColumn id="3" xr3:uid="{53DE22B4-8437-4EA6-813E-2F0CF7E72133}" name="Obiettivo" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{59024008-94B6-47E6-8C7F-69725DFAE6EC}" name="Endpoint" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{DC8ACE73-D608-4E52-81FB-F85282B31F51}" name="Metodo HTTP" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{E583E0AB-6285-4FCA-BC35-0CD0BFB6F457}" name="Payload JSON" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{5BDBA1B2-61ED-47D6-88D1-CDE3D8CC9212}" name="Risultato atteso - Status Code" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{F14E32B9-432F-43ED-9E31-411BF4ADBC3F}" name="Risultato atteso - Dettaglio" dataDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{DFDF46B3-7AFF-4643-9EAB-E56F926CE154}" name="Esito" dataDxfId="27"/>
-    <tableColumn id="10" xr3:uid="{5192CEE0-B98B-4E21-8BEA-8F62C2DAC458}" name="Risultato ottenuto" dataDxfId="26"/>
-    <tableColumn id="11" xr3:uid="{E9C64C9D-7B98-4D7D-8A82-64CB9D831A1C}" name="Screenshot" dataDxfId="25"/>
-    <tableColumn id="12" xr3:uid="{D98AF63F-322C-4828-B53E-197F74FEE6FE}" name="Note" dataDxfId="24"/>
+    <tableColumn id="1" xr3:uid="{3860FCCE-8AB2-4BA5-A927-55A78AF301A2}" name="ID Test" dataDxfId="64"/>
+    <tableColumn id="2" xr3:uid="{6B8298D4-C558-435B-BC50-DF9FF417402B}" name="Area" dataDxfId="63"/>
+    <tableColumn id="3" xr3:uid="{53DE22B4-8437-4EA6-813E-2F0CF7E72133}" name="Obiettivo" dataDxfId="62"/>
+    <tableColumn id="4" xr3:uid="{59024008-94B6-47E6-8C7F-69725DFAE6EC}" name="Endpoint" dataDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{DC8ACE73-D608-4E52-81FB-F85282B31F51}" name="Metodo HTTP" dataDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{E583E0AB-6285-4FCA-BC35-0CD0BFB6F457}" name="Payload JSON" dataDxfId="59"/>
+    <tableColumn id="7" xr3:uid="{5BDBA1B2-61ED-47D6-88D1-CDE3D8CC9212}" name="Risultato atteso - Status Code" dataDxfId="58"/>
+    <tableColumn id="8" xr3:uid="{F14E32B9-432F-43ED-9E31-411BF4ADBC3F}" name="Risultato atteso - Dettaglio" dataDxfId="57"/>
+    <tableColumn id="9" xr3:uid="{DFDF46B3-7AFF-4643-9EAB-E56F926CE154}" name="Esito" dataDxfId="56"/>
+    <tableColumn id="10" xr3:uid="{5192CEE0-B98B-4E21-8BEA-8F62C2DAC458}" name="Risultato ottenuto" dataDxfId="55"/>
+    <tableColumn id="11" xr3:uid="{E9C64C9D-7B98-4D7D-8A82-64CB9D831A1C}" name="Screenshot" dataDxfId="54"/>
+    <tableColumn id="12" xr3:uid="{D98AF63F-322C-4828-B53E-197F74FEE6FE}" name="Note" dataDxfId="53"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5EC5406F-ABEC-4C5A-BB6C-648C616B89A5}" name="Table13" displayName="Table13" ref="A1:L24" totalsRowShown="0" headerRowDxfId="23" dataDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5EC5406F-ABEC-4C5A-BB6C-648C616B89A5}" name="Table13" displayName="Table13" ref="A1:L24" totalsRowShown="0" headerRowDxfId="52" dataDxfId="51">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{5009D189-63E8-4852-A288-87D6EC1E7033}" name="ID Test" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{84642470-32B1-46DB-88F2-1BC4AE8F75C8}" name="Area" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{4F14914F-A3C4-4267-A392-EC2D02D6ADDF}" name="Obiettivo" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{62A87606-C1B8-47E6-9530-D288374DCDF3}" name="Endpoint" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{19E09EE6-EB67-45CF-9A03-E0F0523DB6A0}" name="Metodo HTTP" dataDxfId="17"/>
-    <tableColumn id="6" xr3:uid="{A7AC84FA-A2F1-4930-BDDD-E380EE204368}" name="Payload JSON" dataDxfId="16"/>
-    <tableColumn id="7" xr3:uid="{25C18B10-E594-4E87-AD84-2A557086D8F7}" name="Risultato atteso - Status Code" dataDxfId="15"/>
-    <tableColumn id="8" xr3:uid="{94B79096-6200-43FE-8F50-1C48EB575740}" name="Risultato atteso - Dettaglio" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{AD4E1447-793D-4E65-9313-6A19D961F6AE}" name="Esito" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{B18252F9-BB1D-47B7-8E2C-F42387EC3664}" name="Risultato ottenuto" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{15A8AB07-0563-4A1C-839B-92039F98E2D5}" name="Screenshot" dataDxfId="14"/>
-    <tableColumn id="12" xr3:uid="{4BA21C77-65A7-407A-A5E1-0AA6154386E8}" name="Note" dataDxfId="13"/>
+    <tableColumn id="1" xr3:uid="{5009D189-63E8-4852-A288-87D6EC1E7033}" name="ID Test" dataDxfId="50"/>
+    <tableColumn id="2" xr3:uid="{84642470-32B1-46DB-88F2-1BC4AE8F75C8}" name="Area" dataDxfId="49"/>
+    <tableColumn id="3" xr3:uid="{4F14914F-A3C4-4267-A392-EC2D02D6ADDF}" name="Obiettivo" dataDxfId="48"/>
+    <tableColumn id="4" xr3:uid="{62A87606-C1B8-47E6-9530-D288374DCDF3}" name="Endpoint" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{19E09EE6-EB67-45CF-9A03-E0F0523DB6A0}" name="Metodo HTTP" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{A7AC84FA-A2F1-4930-BDDD-E380EE204368}" name="Payload JSON" dataDxfId="45"/>
+    <tableColumn id="7" xr3:uid="{25C18B10-E594-4E87-AD84-2A557086D8F7}" name="Risultato atteso - Status Code" dataDxfId="44"/>
+    <tableColumn id="8" xr3:uid="{94B79096-6200-43FE-8F50-1C48EB575740}" name="Risultato atteso - Dettaglio" dataDxfId="43"/>
+    <tableColumn id="9" xr3:uid="{AD4E1447-793D-4E65-9313-6A19D961F6AE}" name="Esito" dataDxfId="42"/>
+    <tableColumn id="10" xr3:uid="{B18252F9-BB1D-47B7-8E2C-F42387EC3664}" name="Risultato ottenuto" dataDxfId="41"/>
+    <tableColumn id="11" xr3:uid="{15A8AB07-0563-4A1C-839B-92039F98E2D5}" name="Screenshot" dataDxfId="40"/>
+    <tableColumn id="12" xr3:uid="{4BA21C77-65A7-407A-A5E1-0AA6154386E8}" name="Note" dataDxfId="39"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3C84183B-2219-4217-B03E-3888C2A1762E}" name="Table134" displayName="Table134" ref="A1:L24" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+  <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{B704E338-5C37-41FB-8C85-99D253E12A36}" name="ID Test" dataDxfId="27"/>
+    <tableColumn id="2" xr3:uid="{B2981A3F-A838-4564-95CD-018029141FE3}" name="Area" dataDxfId="26"/>
+    <tableColumn id="3" xr3:uid="{3A09ED62-C911-40F8-84B2-95FDC9F0E73C}" name="Obiettivo" dataDxfId="25"/>
+    <tableColumn id="4" xr3:uid="{7D97DC0F-3E73-4208-8A63-D6DE3FC761AA}" name="Endpoint" dataDxfId="24"/>
+    <tableColumn id="5" xr3:uid="{FF0C5D75-36E7-48D4-A80F-888A5CC255B7}" name="Metodo HTTP" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{023149CE-2E87-48C5-89F0-C06C9BB739DA}" name="Payload JSON" dataDxfId="22"/>
+    <tableColumn id="7" xr3:uid="{8BAEE933-7939-4263-9D14-00FEC91A9C1B}" name="Risultato atteso - Status Code" dataDxfId="21"/>
+    <tableColumn id="8" xr3:uid="{8D31C62B-63D8-4839-9FA3-50CF6221E2BA}" name="Risultato atteso - Dettaglio" dataDxfId="20"/>
+    <tableColumn id="9" xr3:uid="{718B97BF-78C2-4F95-B210-9079004CD606}" name="Esito" dataDxfId="19"/>
+    <tableColumn id="10" xr3:uid="{5CFD81E3-BB64-412E-85AA-84B4611A7F83}" name="Risultato ottenuto" dataDxfId="18"/>
+    <tableColumn id="11" xr3:uid="{6A9BDE4A-CBAC-4363-A060-8EA060236295}" name="Screenshot" dataDxfId="17"/>
+    <tableColumn id="12" xr3:uid="{4E358191-7A4E-4452-AC66-1FBA8A472BD5}" name="Note" dataDxfId="16"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5392533B-6B0E-4F8C-A890-54E0F381453F}" name="Table1345" displayName="Table1345" ref="A1:L24" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+  <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{5DB9B359-E545-4837-92D9-C3F683AC6170}" name="ID Test" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{3357AA3D-D573-45C9-9E54-169DE6BCCC7B}" name="Area" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{FE4BC87A-DD7A-4AC5-9DF0-39C04CF1DEDC}" name="Obiettivo" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{61F99A4D-AC1D-4AAE-BD37-39FC313ECF7E}" name="Endpoint" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{5FD12983-51FF-4BBD-B2DE-46FBD352051D}" name="Metodo HTTP" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{B67C064B-9915-4F2D-8311-0F58E542AA8C}" name="Payload JSON" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{8875AB99-AAA8-46E7-8416-18C1D1E6E0D6}" name="Risultato atteso - Status Code" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{6DA0A166-C4F1-4D89-874B-4007FF063015}" name="Risultato atteso - Dettaglio" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{C4E9099C-524E-4645-AE6E-B8ACEAF227A2}" name="Esito" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{8329D30F-DF3B-4467-8F69-F9BE9E265DCA}" name="Risultato ottenuto" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{99A837AC-AC32-4D7E-BCA2-CEC29E347BE5}" name="Screenshot" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{05FA14BC-760C-4AFA-975E-E185779DFF89}" name="Note" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2354,10 +2530,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2376,7 +2552,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27CCBE7D-F26A-41C6-96A8-43D2BF97BCE3}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultColWidth="91.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -2454,20 +2630,50 @@
         <v>135</v>
       </c>
     </row>
+    <row r="3" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D2">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+  <conditionalFormatting sqref="D2:D3">
+    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
       <formula>"BASSA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
       <formula>"MEDIA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="34" priority="3" operator="equal">
       <formula>"ALTA"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2" xr:uid="{78C482C4-A569-4755-A44B-F5FA399B9D9D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3" xr:uid="{78C482C4-A569-4755-A44B-F5FA399B9D9D}">
       <formula1>"ALTA,MEDIA,BASSA"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3262,10 +3468,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="32" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3280,4 +3486,1615 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C20C51C6-6E6F-4215-9FA0-CAF40473805B}">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="29" style="2" customWidth="1"/>
+    <col min="8" max="8" width="41.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="41.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="58.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="64" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I24">
+    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
+      <formula>"KO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I24" xr:uid="{D757978B-CD58-47E6-82A0-86878BFDB70A}">
+      <formula1>"OK,KO"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2BEB9BE-D1E1-427B-A8AB-8E7466BA14C6}">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="85.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="29" style="2" customWidth="1"/>
+    <col min="8" max="8" width="41.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="41.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="58.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="64" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="L23" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="L24" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I24">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+      <formula>"KO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I24" xr:uid="{C6C44458-0CCE-4CF1-A06A-1FBD3698EB51}">
+      <formula1>"OK,KO"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/docs/testbook/ClinicaFlow_TestBook_API.xlsx
+++ b/docs/testbook/ClinicaFlow_TestBook_API.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\valen\clinicaflow\docs\testbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99819984-289C-4DA6-AE98-9D390E4B0077}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83976FBE-77E6-4384-9BBB-69792E27FE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-4770" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{1C9960E8-B103-4EFA-9509-2FD0D5F86CF0}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="175">
   <si>
     <t>ID Test</t>
   </si>
@@ -560,6 +560,9 @@
   </si>
   <si>
     <t>TC07_CreatePatient_Success.png</t>
+  </si>
+  <si>
+    <t>TS3_20260321</t>
   </si>
 </sst>
 </file>
@@ -1118,7 +1121,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1155,9 +1158,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1206,48 +1206,6 @@
   </cellStyles>
   <dxfs count="67">
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
@@ -1262,48 +1220,6 @@
       </fill>
     </dxf>
     <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill>
           <bgColor rgb="FFFF0000"/>
@@ -1365,6 +1281,90 @@
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1506,42 +1506,42 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3C84183B-2219-4217-B03E-3888C2A1762E}" name="Table134" displayName="Table134" ref="A1:L24" totalsRowShown="0" headerRowDxfId="29" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3C84183B-2219-4217-B03E-3888C2A1762E}" name="Table134" displayName="Table134" ref="A1:L24" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{B704E338-5C37-41FB-8C85-99D253E12A36}" name="ID Test" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{B2981A3F-A838-4564-95CD-018029141FE3}" name="Area" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{3A09ED62-C911-40F8-84B2-95FDC9F0E73C}" name="Obiettivo" dataDxfId="25"/>
-    <tableColumn id="4" xr3:uid="{7D97DC0F-3E73-4208-8A63-D6DE3FC761AA}" name="Endpoint" dataDxfId="24"/>
-    <tableColumn id="5" xr3:uid="{FF0C5D75-36E7-48D4-A80F-888A5CC255B7}" name="Metodo HTTP" dataDxfId="23"/>
-    <tableColumn id="6" xr3:uid="{023149CE-2E87-48C5-89F0-C06C9BB739DA}" name="Payload JSON" dataDxfId="22"/>
-    <tableColumn id="7" xr3:uid="{8BAEE933-7939-4263-9D14-00FEC91A9C1B}" name="Risultato atteso - Status Code" dataDxfId="21"/>
-    <tableColumn id="8" xr3:uid="{8D31C62B-63D8-4839-9FA3-50CF6221E2BA}" name="Risultato atteso - Dettaglio" dataDxfId="20"/>
-    <tableColumn id="9" xr3:uid="{718B97BF-78C2-4F95-B210-9079004CD606}" name="Esito" dataDxfId="19"/>
-    <tableColumn id="10" xr3:uid="{5CFD81E3-BB64-412E-85AA-84B4611A7F83}" name="Risultato ottenuto" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{6A9BDE4A-CBAC-4363-A060-8EA060236295}" name="Screenshot" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{4E358191-7A4E-4452-AC66-1FBA8A472BD5}" name="Note" dataDxfId="16"/>
+    <tableColumn id="1" xr3:uid="{B704E338-5C37-41FB-8C85-99D253E12A36}" name="ID Test" dataDxfId="36"/>
+    <tableColumn id="2" xr3:uid="{B2981A3F-A838-4564-95CD-018029141FE3}" name="Area" dataDxfId="35"/>
+    <tableColumn id="3" xr3:uid="{3A09ED62-C911-40F8-84B2-95FDC9F0E73C}" name="Obiettivo" dataDxfId="34"/>
+    <tableColumn id="4" xr3:uid="{7D97DC0F-3E73-4208-8A63-D6DE3FC761AA}" name="Endpoint" dataDxfId="33"/>
+    <tableColumn id="5" xr3:uid="{FF0C5D75-36E7-48D4-A80F-888A5CC255B7}" name="Metodo HTTP" dataDxfId="32"/>
+    <tableColumn id="6" xr3:uid="{023149CE-2E87-48C5-89F0-C06C9BB739DA}" name="Payload JSON" dataDxfId="31"/>
+    <tableColumn id="7" xr3:uid="{8BAEE933-7939-4263-9D14-00FEC91A9C1B}" name="Risultato atteso - Status Code" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{8D31C62B-63D8-4839-9FA3-50CF6221E2BA}" name="Risultato atteso - Dettaglio" dataDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{718B97BF-78C2-4F95-B210-9079004CD606}" name="Esito" dataDxfId="28"/>
+    <tableColumn id="10" xr3:uid="{5CFD81E3-BB64-412E-85AA-84B4611A7F83}" name="Risultato ottenuto" dataDxfId="27"/>
+    <tableColumn id="11" xr3:uid="{6A9BDE4A-CBAC-4363-A060-8EA060236295}" name="Screenshot" dataDxfId="26"/>
+    <tableColumn id="12" xr3:uid="{4E358191-7A4E-4452-AC66-1FBA8A472BD5}" name="Note" dataDxfId="25"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5392533B-6B0E-4F8C-A890-54E0F381453F}" name="Table1345" displayName="Table1345" ref="A1:L24" totalsRowShown="0" headerRowDxfId="13" dataDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5392533B-6B0E-4F8C-A890-54E0F381453F}" name="Table1345" displayName="Table1345" ref="A1:L24" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{5DB9B359-E545-4837-92D9-C3F683AC6170}" name="ID Test" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{3357AA3D-D573-45C9-9E54-169DE6BCCC7B}" name="Area" dataDxfId="10"/>
-    <tableColumn id="3" xr3:uid="{FE4BC87A-DD7A-4AC5-9DF0-39C04CF1DEDC}" name="Obiettivo" dataDxfId="9"/>
-    <tableColumn id="4" xr3:uid="{61F99A4D-AC1D-4AAE-BD37-39FC313ECF7E}" name="Endpoint" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{5FD12983-51FF-4BBD-B2DE-46FBD352051D}" name="Metodo HTTP" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{B67C064B-9915-4F2D-8311-0F58E542AA8C}" name="Payload JSON" dataDxfId="6"/>
-    <tableColumn id="7" xr3:uid="{8875AB99-AAA8-46E7-8416-18C1D1E6E0D6}" name="Risultato atteso - Status Code" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{6DA0A166-C4F1-4D89-874B-4007FF063015}" name="Risultato atteso - Dettaglio" dataDxfId="4"/>
-    <tableColumn id="9" xr3:uid="{C4E9099C-524E-4645-AE6E-B8ACEAF227A2}" name="Esito" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{8329D30F-DF3B-4467-8F69-F9BE9E265DCA}" name="Risultato ottenuto" dataDxfId="2"/>
-    <tableColumn id="11" xr3:uid="{99A837AC-AC32-4D7E-BCA2-CEC29E347BE5}" name="Screenshot" dataDxfId="1"/>
-    <tableColumn id="12" xr3:uid="{05FA14BC-760C-4AFA-975E-E185779DFF89}" name="Note" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{5DB9B359-E545-4837-92D9-C3F683AC6170}" name="ID Test" dataDxfId="22"/>
+    <tableColumn id="2" xr3:uid="{3357AA3D-D573-45C9-9E54-169DE6BCCC7B}" name="Area" dataDxfId="21"/>
+    <tableColumn id="3" xr3:uid="{FE4BC87A-DD7A-4AC5-9DF0-39C04CF1DEDC}" name="Obiettivo" dataDxfId="20"/>
+    <tableColumn id="4" xr3:uid="{61F99A4D-AC1D-4AAE-BD37-39FC313ECF7E}" name="Endpoint" dataDxfId="19"/>
+    <tableColumn id="5" xr3:uid="{5FD12983-51FF-4BBD-B2DE-46FBD352051D}" name="Metodo HTTP" dataDxfId="18"/>
+    <tableColumn id="6" xr3:uid="{B67C064B-9915-4F2D-8311-0F58E542AA8C}" name="Payload JSON" dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{8875AB99-AAA8-46E7-8416-18C1D1E6E0D6}" name="Risultato atteso - Status Code" dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{6DA0A166-C4F1-4D89-874B-4007FF063015}" name="Risultato atteso - Dettaglio" dataDxfId="15"/>
+    <tableColumn id="9" xr3:uid="{C4E9099C-524E-4645-AE6E-B8ACEAF227A2}" name="Esito" dataDxfId="14"/>
+    <tableColumn id="10" xr3:uid="{8329D30F-DF3B-4467-8F69-F9BE9E265DCA}" name="Risultato ottenuto" dataDxfId="13"/>
+    <tableColumn id="11" xr3:uid="{99A837AC-AC32-4D7E-BCA2-CEC29E347BE5}" name="Screenshot" dataDxfId="12"/>
+    <tableColumn id="12" xr3:uid="{05FA14BC-760C-4AFA-975E-E185779DFF89}" name="Note" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2530,10 +2530,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="38" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="37" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2616,7 +2616,9 @@
       <c r="E2" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="F2" s="8"/>
+      <c r="F2" s="8" t="s">
+        <v>170</v>
+      </c>
       <c r="G2" s="8" t="s">
         <v>112</v>
       </c>
@@ -2646,29 +2648,31 @@
       <c r="E3" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="F3" s="8"/>
+      <c r="F3" s="8" t="s">
+        <v>174</v>
+      </c>
       <c r="G3" s="8" t="s">
         <v>112</v>
       </c>
       <c r="H3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="9" t="s">
         <v>167</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D3">
-    <cfRule type="cellIs" dxfId="36" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"BASSA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="35" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"MEDIA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
       <formula>"ALTA"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3468,10 +3472,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="33" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="32" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4275,10 +4279,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="31" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5079,10 +5083,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/docs/testbook/ClinicaFlow_TestBook_API.xlsx
+++ b/docs/testbook/ClinicaFlow_TestBook_API.xlsx
@@ -8,23 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\valen\clinicaflow\docs\testbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83976FBE-77E6-4384-9BBB-69792E27FE2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D468709-F195-48D9-8F1A-5DC95484EE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-4770" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{1C9960E8-B103-4EFA-9509-2FD0D5F86CF0}"/>
+    <workbookView xWindow="20370" yWindow="-4770" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{1C9960E8-B103-4EFA-9509-2FD0D5F86CF0}"/>
   </bookViews>
   <sheets>
     <sheet name="ClinicaFlow_TestBook_API" sheetId="1" r:id="rId1"/>
-    <sheet name="BUG" sheetId="3" r:id="rId2"/>
-    <sheet name="TS1_20260321" sheetId="2" r:id="rId3"/>
-    <sheet name="TS2_20260321" sheetId="4" r:id="rId4"/>
-    <sheet name="TS3_20260321" sheetId="5" r:id="rId5"/>
+    <sheet name="TS1_20260321" sheetId="2" r:id="rId2"/>
+    <sheet name="TS2_20260321" sheetId="4" r:id="rId3"/>
+    <sheet name="TS3_20260321" sheetId="5" r:id="rId4"/>
+    <sheet name="TS4_20260322" sheetId="6" r:id="rId5"/>
+    <sheet name="TS5_20260322" sheetId="7" r:id="rId6"/>
+    <sheet name="BUG" sheetId="3" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="195">
   <si>
     <t>ID Test</t>
   </si>
@@ -266,9 +268,6 @@
     <t>L'appuntamento restituito ha stato Completed.</t>
   </si>
   <si>
-    <t xml:space="preserve"> "TC15_GetCompletedAppointment_Success.png"</t>
-  </si>
-  <si>
     <t>TC16</t>
   </si>
   <si>
@@ -278,9 +277,6 @@
     <t>Il referto viene creato correttamente.</t>
   </si>
   <si>
-    <t xml:space="preserve"> "TC16_CreateMedicalReport_Success.png"</t>
-  </si>
-  <si>
     <t>TC17</t>
   </si>
   <si>
@@ -290,9 +286,6 @@
     <t>{"appointmentId":1,"diagnosis":"Test di duplicazione referto","therapy":"Non applicabile","notes":"Secondo referto non consentito"}</t>
   </si>
   <si>
-    <t xml:space="preserve"> "TC17_CreateDuplicateMedicalReport_Conflict.png"</t>
-  </si>
-  <si>
     <t>TC18</t>
   </si>
   <si>
@@ -348,9 +341,6 @@
   </si>
   <si>
     <t>TC23</t>
-  </si>
-  <si>
-    <t>Verificare il ripristino della disponibilitÃ  dello slot dopo l'annullamento dell'appuntamento.</t>
   </si>
   <si>
     <t>Lo slot restituito ha isAvailable = true.</t>
@@ -563,6 +553,96 @@
   </si>
   <si>
     <t>TS3_20260321</t>
+  </si>
+  <si>
+    <t>Microsoft.Data.SqlClient.SqlException : Cannot insert the value NULL into column 'AppointmentDate', table 'ClinicaFlowDb.dbo.Appointments'; column does not allow nulls. INSERT fails.</t>
+  </si>
+  <si>
+    <t>{"patientId":3,"availabilitySlotId":1,"notes":"Prima visita cardiologica"}</t>
+  </si>
+  <si>
+    <t>BUG03</t>
+  </si>
+  <si>
+    <t>TS4_20260322</t>
+  </si>
+  <si>
+    <t>TS5_20260322</t>
+  </si>
+  <si>
+    <t>Appuntamento creato correttamente.</t>
+  </si>
+  <si>
+    <t>Lo slot selezionato non è più disponibile.</t>
+  </si>
+  <si>
+    <t>/api/appointments/4/status</t>
+  </si>
+  <si>
+    <t>Stato dell'appuntamento aggiornato correttamente</t>
+  </si>
+  <si>
+    <t>TC15_GetCompletedAppointment_Success.png</t>
+  </si>
+  <si>
+    <t>TC16_CreateMedicalReport_Success.png</t>
+  </si>
+  <si>
+    <t>TC17_CreateDuplicateMedicalReport_Conflict.png</t>
+  </si>
+  <si>
+    <t>{"appointmentId":4,"diagnosis":"Ipertensione lieve","therapy":"Ridurre il consumo di sale e monitorare la pressione arteriosa","notes":"Controllo consigliato tra 30 giorni"}</t>
+  </si>
+  <si>
+    <t>Referto creato correttamente</t>
+  </si>
+  <si>
+    <t>{"appointmentId":4,"diagnosis":"Test di duplicazione referto","therapy":"Non applicabile","notes":"Secondo referto non consentito"}</t>
+  </si>
+  <si>
+    <t>Esiste già un referto associato a questo appuntamento.</t>
+  </si>
+  <si>
+    <t>/api/medicalreports/by-appointment/4</t>
+  </si>
+  <si>
+    <t>Referto recuperato correttamente</t>
+  </si>
+  <si>
+    <t>/api/appointments/5/status</t>
+  </si>
+  <si>
+    <t>Verificare il ripristino della disponibilità dello slot dopo l'annullamento dell'appuntamento.</t>
+  </si>
+  <si>
+    <t>{
+  "patientId": 3,
+  "doctorId": 1,
+  "availabilitySlotId": 1,
+  "notes": "Tentativo di seconda prenotazione"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "patientId": 3,
+  "availabilitySlotId": 2,
+  "notes": "Visita di controllo cardiologico"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "patientId": 3,
+  "availabilitySlotId": 1,
+  "notes": "Prima visita cardiologica"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "patientId": 3,
+  "availabilitySlotId": 1,
+  "appointmentDate": "2026-03-22T10:30:00",
+  "notes": "Prima visita cardiologica"
+}</t>
   </si>
 </sst>
 </file>
@@ -1157,7 +1237,7 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1204,7 +1284,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="67">
+  <dxfs count="99">
     <dxf>
       <fill>
         <patternFill>
@@ -1215,7 +1295,14 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FF92D050"/>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1257,14 +1344,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1281,6 +1361,118 @@
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1464,84 +1656,126 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}" name="Table1" displayName="Table1" ref="A1:L24" totalsRowShown="0" headerRowDxfId="66" dataDxfId="65">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}" name="Table1" displayName="Table1" ref="A1:L24" totalsRowShown="0" headerRowDxfId="98" dataDxfId="97">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{3860FCCE-8AB2-4BA5-A927-55A78AF301A2}" name="ID Test" dataDxfId="64"/>
-    <tableColumn id="2" xr3:uid="{6B8298D4-C558-435B-BC50-DF9FF417402B}" name="Area" dataDxfId="63"/>
-    <tableColumn id="3" xr3:uid="{53DE22B4-8437-4EA6-813E-2F0CF7E72133}" name="Obiettivo" dataDxfId="62"/>
-    <tableColumn id="4" xr3:uid="{59024008-94B6-47E6-8C7F-69725DFAE6EC}" name="Endpoint" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{DC8ACE73-D608-4E52-81FB-F85282B31F51}" name="Metodo HTTP" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{E583E0AB-6285-4FCA-BC35-0CD0BFB6F457}" name="Payload JSON" dataDxfId="59"/>
-    <tableColumn id="7" xr3:uid="{5BDBA1B2-61ED-47D6-88D1-CDE3D8CC9212}" name="Risultato atteso - Status Code" dataDxfId="58"/>
-    <tableColumn id="8" xr3:uid="{F14E32B9-432F-43ED-9E31-411BF4ADBC3F}" name="Risultato atteso - Dettaglio" dataDxfId="57"/>
-    <tableColumn id="9" xr3:uid="{DFDF46B3-7AFF-4643-9EAB-E56F926CE154}" name="Esito" dataDxfId="56"/>
-    <tableColumn id="10" xr3:uid="{5192CEE0-B98B-4E21-8BEA-8F62C2DAC458}" name="Risultato ottenuto" dataDxfId="55"/>
-    <tableColumn id="11" xr3:uid="{E9C64C9D-7B98-4D7D-8A82-64CB9D831A1C}" name="Screenshot" dataDxfId="54"/>
-    <tableColumn id="12" xr3:uid="{D98AF63F-322C-4828-B53E-197F74FEE6FE}" name="Note" dataDxfId="53"/>
+    <tableColumn id="1" xr3:uid="{3860FCCE-8AB2-4BA5-A927-55A78AF301A2}" name="ID Test" dataDxfId="96"/>
+    <tableColumn id="2" xr3:uid="{6B8298D4-C558-435B-BC50-DF9FF417402B}" name="Area" dataDxfId="95"/>
+    <tableColumn id="3" xr3:uid="{53DE22B4-8437-4EA6-813E-2F0CF7E72133}" name="Obiettivo" dataDxfId="94"/>
+    <tableColumn id="4" xr3:uid="{59024008-94B6-47E6-8C7F-69725DFAE6EC}" name="Endpoint" dataDxfId="93"/>
+    <tableColumn id="5" xr3:uid="{DC8ACE73-D608-4E52-81FB-F85282B31F51}" name="Metodo HTTP" dataDxfId="92"/>
+    <tableColumn id="6" xr3:uid="{E583E0AB-6285-4FCA-BC35-0CD0BFB6F457}" name="Payload JSON" dataDxfId="91"/>
+    <tableColumn id="7" xr3:uid="{5BDBA1B2-61ED-47D6-88D1-CDE3D8CC9212}" name="Risultato atteso - Status Code" dataDxfId="90"/>
+    <tableColumn id="8" xr3:uid="{F14E32B9-432F-43ED-9E31-411BF4ADBC3F}" name="Risultato atteso - Dettaglio" dataDxfId="89"/>
+    <tableColumn id="9" xr3:uid="{DFDF46B3-7AFF-4643-9EAB-E56F926CE154}" name="Esito" dataDxfId="88"/>
+    <tableColumn id="10" xr3:uid="{5192CEE0-B98B-4E21-8BEA-8F62C2DAC458}" name="Risultato ottenuto" dataDxfId="87"/>
+    <tableColumn id="11" xr3:uid="{E9C64C9D-7B98-4D7D-8A82-64CB9D831A1C}" name="Screenshot" dataDxfId="86"/>
+    <tableColumn id="12" xr3:uid="{D98AF63F-322C-4828-B53E-197F74FEE6FE}" name="Note" dataDxfId="85"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5EC5406F-ABEC-4C5A-BB6C-648C616B89A5}" name="Table13" displayName="Table13" ref="A1:L24" totalsRowShown="0" headerRowDxfId="52" dataDxfId="51">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5EC5406F-ABEC-4C5A-BB6C-648C616B89A5}" name="Table13" displayName="Table13" ref="A1:L24" totalsRowShown="0" headerRowDxfId="84" dataDxfId="83">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{5009D189-63E8-4852-A288-87D6EC1E7033}" name="ID Test" dataDxfId="50"/>
-    <tableColumn id="2" xr3:uid="{84642470-32B1-46DB-88F2-1BC4AE8F75C8}" name="Area" dataDxfId="49"/>
-    <tableColumn id="3" xr3:uid="{4F14914F-A3C4-4267-A392-EC2D02D6ADDF}" name="Obiettivo" dataDxfId="48"/>
-    <tableColumn id="4" xr3:uid="{62A87606-C1B8-47E6-9530-D288374DCDF3}" name="Endpoint" dataDxfId="47"/>
-    <tableColumn id="5" xr3:uid="{19E09EE6-EB67-45CF-9A03-E0F0523DB6A0}" name="Metodo HTTP" dataDxfId="46"/>
-    <tableColumn id="6" xr3:uid="{A7AC84FA-A2F1-4930-BDDD-E380EE204368}" name="Payload JSON" dataDxfId="45"/>
-    <tableColumn id="7" xr3:uid="{25C18B10-E594-4E87-AD84-2A557086D8F7}" name="Risultato atteso - Status Code" dataDxfId="44"/>
-    <tableColumn id="8" xr3:uid="{94B79096-6200-43FE-8F50-1C48EB575740}" name="Risultato atteso - Dettaglio" dataDxfId="43"/>
-    <tableColumn id="9" xr3:uid="{AD4E1447-793D-4E65-9313-6A19D961F6AE}" name="Esito" dataDxfId="42"/>
-    <tableColumn id="10" xr3:uid="{B18252F9-BB1D-47B7-8E2C-F42387EC3664}" name="Risultato ottenuto" dataDxfId="41"/>
-    <tableColumn id="11" xr3:uid="{15A8AB07-0563-4A1C-839B-92039F98E2D5}" name="Screenshot" dataDxfId="40"/>
-    <tableColumn id="12" xr3:uid="{4BA21C77-65A7-407A-A5E1-0AA6154386E8}" name="Note" dataDxfId="39"/>
+    <tableColumn id="1" xr3:uid="{5009D189-63E8-4852-A288-87D6EC1E7033}" name="ID Test" dataDxfId="82"/>
+    <tableColumn id="2" xr3:uid="{84642470-32B1-46DB-88F2-1BC4AE8F75C8}" name="Area" dataDxfId="81"/>
+    <tableColumn id="3" xr3:uid="{4F14914F-A3C4-4267-A392-EC2D02D6ADDF}" name="Obiettivo" dataDxfId="80"/>
+    <tableColumn id="4" xr3:uid="{62A87606-C1B8-47E6-9530-D288374DCDF3}" name="Endpoint" dataDxfId="79"/>
+    <tableColumn id="5" xr3:uid="{19E09EE6-EB67-45CF-9A03-E0F0523DB6A0}" name="Metodo HTTP" dataDxfId="78"/>
+    <tableColumn id="6" xr3:uid="{A7AC84FA-A2F1-4930-BDDD-E380EE204368}" name="Payload JSON" dataDxfId="77"/>
+    <tableColumn id="7" xr3:uid="{25C18B10-E594-4E87-AD84-2A557086D8F7}" name="Risultato atteso - Status Code" dataDxfId="76"/>
+    <tableColumn id="8" xr3:uid="{94B79096-6200-43FE-8F50-1C48EB575740}" name="Risultato atteso - Dettaglio" dataDxfId="75"/>
+    <tableColumn id="9" xr3:uid="{AD4E1447-793D-4E65-9313-6A19D961F6AE}" name="Esito" dataDxfId="74"/>
+    <tableColumn id="10" xr3:uid="{B18252F9-BB1D-47B7-8E2C-F42387EC3664}" name="Risultato ottenuto" dataDxfId="73"/>
+    <tableColumn id="11" xr3:uid="{15A8AB07-0563-4A1C-839B-92039F98E2D5}" name="Screenshot" dataDxfId="72"/>
+    <tableColumn id="12" xr3:uid="{4BA21C77-65A7-407A-A5E1-0AA6154386E8}" name="Note" dataDxfId="71"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3C84183B-2219-4217-B03E-3888C2A1762E}" name="Table134" displayName="Table134" ref="A1:L24" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3C84183B-2219-4217-B03E-3888C2A1762E}" name="Table134" displayName="Table134" ref="A1:L24" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{B704E338-5C37-41FB-8C85-99D253E12A36}" name="ID Test" dataDxfId="36"/>
-    <tableColumn id="2" xr3:uid="{B2981A3F-A838-4564-95CD-018029141FE3}" name="Area" dataDxfId="35"/>
-    <tableColumn id="3" xr3:uid="{3A09ED62-C911-40F8-84B2-95FDC9F0E73C}" name="Obiettivo" dataDxfId="34"/>
-    <tableColumn id="4" xr3:uid="{7D97DC0F-3E73-4208-8A63-D6DE3FC761AA}" name="Endpoint" dataDxfId="33"/>
-    <tableColumn id="5" xr3:uid="{FF0C5D75-36E7-48D4-A80F-888A5CC255B7}" name="Metodo HTTP" dataDxfId="32"/>
-    <tableColumn id="6" xr3:uid="{023149CE-2E87-48C5-89F0-C06C9BB739DA}" name="Payload JSON" dataDxfId="31"/>
-    <tableColumn id="7" xr3:uid="{8BAEE933-7939-4263-9D14-00FEC91A9C1B}" name="Risultato atteso - Status Code" dataDxfId="30"/>
-    <tableColumn id="8" xr3:uid="{8D31C62B-63D8-4839-9FA3-50CF6221E2BA}" name="Risultato atteso - Dettaglio" dataDxfId="29"/>
-    <tableColumn id="9" xr3:uid="{718B97BF-78C2-4F95-B210-9079004CD606}" name="Esito" dataDxfId="28"/>
-    <tableColumn id="10" xr3:uid="{5CFD81E3-BB64-412E-85AA-84B4611A7F83}" name="Risultato ottenuto" dataDxfId="27"/>
-    <tableColumn id="11" xr3:uid="{6A9BDE4A-CBAC-4363-A060-8EA060236295}" name="Screenshot" dataDxfId="26"/>
-    <tableColumn id="12" xr3:uid="{4E358191-7A4E-4452-AC66-1FBA8A472BD5}" name="Note" dataDxfId="25"/>
+    <tableColumn id="1" xr3:uid="{B704E338-5C37-41FB-8C85-99D253E12A36}" name="ID Test" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{B2981A3F-A838-4564-95CD-018029141FE3}" name="Area" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{3A09ED62-C911-40F8-84B2-95FDC9F0E73C}" name="Obiettivo" dataDxfId="66"/>
+    <tableColumn id="4" xr3:uid="{7D97DC0F-3E73-4208-8A63-D6DE3FC761AA}" name="Endpoint" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{FF0C5D75-36E7-48D4-A80F-888A5CC255B7}" name="Metodo HTTP" dataDxfId="64"/>
+    <tableColumn id="6" xr3:uid="{023149CE-2E87-48C5-89F0-C06C9BB739DA}" name="Payload JSON" dataDxfId="63"/>
+    <tableColumn id="7" xr3:uid="{8BAEE933-7939-4263-9D14-00FEC91A9C1B}" name="Risultato atteso - Status Code" dataDxfId="62"/>
+    <tableColumn id="8" xr3:uid="{8D31C62B-63D8-4839-9FA3-50CF6221E2BA}" name="Risultato atteso - Dettaglio" dataDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{718B97BF-78C2-4F95-B210-9079004CD606}" name="Esito" dataDxfId="60"/>
+    <tableColumn id="10" xr3:uid="{5CFD81E3-BB64-412E-85AA-84B4611A7F83}" name="Risultato ottenuto" dataDxfId="59"/>
+    <tableColumn id="11" xr3:uid="{6A9BDE4A-CBAC-4363-A060-8EA060236295}" name="Screenshot" dataDxfId="58"/>
+    <tableColumn id="12" xr3:uid="{4E358191-7A4E-4452-AC66-1FBA8A472BD5}" name="Note" dataDxfId="57"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5392533B-6B0E-4F8C-A890-54E0F381453F}" name="Table1345" displayName="Table1345" ref="A1:L24" totalsRowShown="0" headerRowDxfId="24" dataDxfId="23">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5392533B-6B0E-4F8C-A890-54E0F381453F}" name="Table1345" displayName="Table1345" ref="A1:L24" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{5DB9B359-E545-4837-92D9-C3F683AC6170}" name="ID Test" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{3357AA3D-D573-45C9-9E54-169DE6BCCC7B}" name="Area" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{FE4BC87A-DD7A-4AC5-9DF0-39C04CF1DEDC}" name="Obiettivo" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{61F99A4D-AC1D-4AAE-BD37-39FC313ECF7E}" name="Endpoint" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{5FD12983-51FF-4BBD-B2DE-46FBD352051D}" name="Metodo HTTP" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{B67C064B-9915-4F2D-8311-0F58E542AA8C}" name="Payload JSON" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{8875AB99-AAA8-46E7-8416-18C1D1E6E0D6}" name="Risultato atteso - Status Code" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{6DA0A166-C4F1-4D89-874B-4007FF063015}" name="Risultato atteso - Dettaglio" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{C4E9099C-524E-4645-AE6E-B8ACEAF227A2}" name="Esito" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{8329D30F-DF3B-4467-8F69-F9BE9E265DCA}" name="Risultato ottenuto" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{99A837AC-AC32-4D7E-BCA2-CEC29E347BE5}" name="Screenshot" dataDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{05FA14BC-760C-4AFA-975E-E185779DFF89}" name="Note" dataDxfId="11"/>
+    <tableColumn id="1" xr3:uid="{5DB9B359-E545-4837-92D9-C3F683AC6170}" name="ID Test" dataDxfId="54"/>
+    <tableColumn id="2" xr3:uid="{3357AA3D-D573-45C9-9E54-169DE6BCCC7B}" name="Area" dataDxfId="53"/>
+    <tableColumn id="3" xr3:uid="{FE4BC87A-DD7A-4AC5-9DF0-39C04CF1DEDC}" name="Obiettivo" dataDxfId="52"/>
+    <tableColumn id="4" xr3:uid="{61F99A4D-AC1D-4AAE-BD37-39FC313ECF7E}" name="Endpoint" dataDxfId="51"/>
+    <tableColumn id="5" xr3:uid="{5FD12983-51FF-4BBD-B2DE-46FBD352051D}" name="Metodo HTTP" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{B67C064B-9915-4F2D-8311-0F58E542AA8C}" name="Payload JSON" dataDxfId="49"/>
+    <tableColumn id="7" xr3:uid="{8875AB99-AAA8-46E7-8416-18C1D1E6E0D6}" name="Risultato atteso - Status Code" dataDxfId="48"/>
+    <tableColumn id="8" xr3:uid="{6DA0A166-C4F1-4D89-874B-4007FF063015}" name="Risultato atteso - Dettaglio" dataDxfId="47"/>
+    <tableColumn id="9" xr3:uid="{C4E9099C-524E-4645-AE6E-B8ACEAF227A2}" name="Esito" dataDxfId="46"/>
+    <tableColumn id="10" xr3:uid="{8329D30F-DF3B-4467-8F69-F9BE9E265DCA}" name="Risultato ottenuto" dataDxfId="45"/>
+    <tableColumn id="11" xr3:uid="{99A837AC-AC32-4D7E-BCA2-CEC29E347BE5}" name="Screenshot" dataDxfId="44"/>
+    <tableColumn id="12" xr3:uid="{05FA14BC-760C-4AFA-975E-E185779DFF89}" name="Note" dataDxfId="43"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{28F10800-5F17-4DF4-A265-9540A82D8F49}" name="Table13456" displayName="Table13456" ref="A1:L24" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
+  <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{63214038-0043-4A32-AF2E-81FCC7E0E959}" name="ID Test" dataDxfId="40"/>
+    <tableColumn id="2" xr3:uid="{DA94D99B-D0CD-4C28-90D5-7D36DEEDED54}" name="Area" dataDxfId="39"/>
+    <tableColumn id="3" xr3:uid="{860DD01C-3A8E-48EE-9E95-D5ED1A4B8AF3}" name="Obiettivo" dataDxfId="38"/>
+    <tableColumn id="4" xr3:uid="{C311DD5F-6C88-4F21-9480-8419A1D24693}" name="Endpoint" dataDxfId="37"/>
+    <tableColumn id="5" xr3:uid="{AFCD354B-2A4F-412F-8FF0-4E34F43379DC}" name="Metodo HTTP" dataDxfId="36"/>
+    <tableColumn id="6" xr3:uid="{666265C9-EBE4-4901-944B-B821A3D713C8}" name="Payload JSON" dataDxfId="35"/>
+    <tableColumn id="7" xr3:uid="{7AD7F2D9-9A10-474B-A4BA-BF7F2688D184}" name="Risultato atteso - Status Code" dataDxfId="34"/>
+    <tableColumn id="8" xr3:uid="{53F65EF7-BF0C-48A0-BB4B-34BF9E2D6AB7}" name="Risultato atteso - Dettaglio" dataDxfId="33"/>
+    <tableColumn id="9" xr3:uid="{586EA1BD-3E26-4E9F-8B58-99210DFA6D75}" name="Esito" dataDxfId="32"/>
+    <tableColumn id="10" xr3:uid="{FC30B956-A42E-4863-B26D-CD1CE586B61C}" name="Risultato ottenuto" dataDxfId="31"/>
+    <tableColumn id="11" xr3:uid="{38D8A589-74FA-48A3-B607-721851799674}" name="Screenshot" dataDxfId="30"/>
+    <tableColumn id="12" xr3:uid="{2555A3BC-E4BE-4790-A872-4E791D4BE524}" name="Note" dataDxfId="29"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{42FC6E2F-12D2-4B07-83FE-5568C141ED11}" name="Table134567" displayName="Table134567" ref="A1:L24" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
+  <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{4C6B92BD-7AE4-4837-9A54-CCAFFF439227}" name="ID Test" dataDxfId="26"/>
+    <tableColumn id="2" xr3:uid="{46BBB285-C581-46F6-8FD2-761048895C44}" name="Area" dataDxfId="25"/>
+    <tableColumn id="3" xr3:uid="{DAC70DE0-1731-4FF2-904B-BE773769384C}" name="Obiettivo" dataDxfId="24"/>
+    <tableColumn id="4" xr3:uid="{DEB47A3E-0270-48FB-98B6-8A232FDFCFCE}" name="Endpoint" dataDxfId="23"/>
+    <tableColumn id="5" xr3:uid="{71FF2070-0AD2-4FC5-ACAE-A7B00B48E2A7}" name="Metodo HTTP" dataDxfId="22"/>
+    <tableColumn id="6" xr3:uid="{DFAEB569-EFF2-48F3-9456-5279864957F5}" name="Payload JSON" dataDxfId="21"/>
+    <tableColumn id="7" xr3:uid="{CE89C81C-1169-4A34-873C-ED12BB2E88FD}" name="Risultato atteso - Status Code" dataDxfId="20"/>
+    <tableColumn id="8" xr3:uid="{83059EF0-2287-4D73-949B-360391CB89F9}" name="Risultato atteso - Dettaglio" dataDxfId="19"/>
+    <tableColumn id="9" xr3:uid="{EA9E5C2E-4549-44C4-9E4A-438269678451}" name="Esito" dataDxfId="18"/>
+    <tableColumn id="10" xr3:uid="{4979933D-EB34-41F5-8643-936F826A3AF4}" name="Risultato ottenuto" dataDxfId="17"/>
+    <tableColumn id="11" xr3:uid="{22F04AFA-26CC-44FD-9673-D56BEC383839}" name="Screenshot" dataDxfId="16"/>
+    <tableColumn id="12" xr3:uid="{29D1856A-E944-4770-AB5F-BF2439CEDF3E}" name="Note" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1849,7 +2083,7 @@
   <cols>
     <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.7109375" style="2" customWidth="1"/>
     <col min="4" max="4" width="36.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="54.7109375" style="1" customWidth="1"/>
@@ -1911,7 +2145,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>15</v>
@@ -1926,7 +2160,7 @@
         <v>18</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -1940,7 +2174,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>15</v>
@@ -1966,7 +2200,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>15</v>
@@ -1981,7 +2215,7 @@
         <v>26</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -1995,7 +2229,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>29</v>
@@ -2018,22 +2252,22 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2047,7 +2281,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>15</v>
@@ -2059,10 +2293,10 @@
         <v>38</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="60" x14ac:dyDescent="0.25">
@@ -2076,7 +2310,7 @@
         <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>15</v>
@@ -2091,7 +2325,7 @@
         <v>43</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2105,7 +2339,7 @@
         <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>15</v>
@@ -2120,7 +2354,7 @@
         <v>48</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2134,7 +2368,7 @@
         <v>51</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>15</v>
@@ -2146,10 +2380,10 @@
         <v>25</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2163,7 +2397,7 @@
         <v>55</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>15</v>
@@ -2178,7 +2412,7 @@
         <v>57</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2192,7 +2426,7 @@
         <v>60</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>15</v>
@@ -2204,10 +2438,10 @@
         <v>25</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -2221,7 +2455,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>29</v>
@@ -2233,7 +2467,7 @@
         <v>64</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="60" x14ac:dyDescent="0.25">
@@ -2247,7 +2481,7 @@
         <v>68</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>15</v>
@@ -2259,10 +2493,10 @@
         <v>38</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2276,7 +2510,7 @@
         <v>71</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>72</v>
@@ -2302,7 +2536,7 @@
         <v>78</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>29</v>
@@ -2314,21 +2548,21 @@
         <v>79</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>15</v>
@@ -2340,53 +2574,53 @@
         <v>17</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>84</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>88</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>29</v>
@@ -2395,125 +2629,125 @@
         <v>30</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>72</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>108</v>
+      <c r="C24" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>29</v>
@@ -2522,18 +2756,18 @@
         <v>30</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2551,149 +2785,14 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27CCBE7D-F26A-41C6-96A8-43D2BF97BCE3}">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultColWidth="91.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="68.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="89.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="30.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="120" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>162</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>167</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="D2:D3">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
-      <formula>"BASSA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
-      <formula>"MEDIA"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="3" operator="equal">
-      <formula>"ALTA"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D3" xr:uid="{78C482C4-A569-4755-A44B-F5FA399B9D9D}">
-      <formula1>"ALTA,MEDIA,BASSA"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FD9EF9F-CB0B-4D0D-A402-0DE892E54EC1}">
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="22.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="54.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="29" style="2" customWidth="1"/>
@@ -2754,7 +2853,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>15</v>
@@ -2769,13 +2868,13 @@
         <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2789,7 +2888,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>15</v>
@@ -2804,10 +2903,10 @@
         <v>22</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2821,7 +2920,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>15</v>
@@ -2836,13 +2935,13 @@
         <v>26</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2856,7 +2955,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>29</v>
@@ -2868,10 +2967,10 @@
         <v>31</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2885,31 +2984,31 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2923,7 +3022,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>15</v>
@@ -2935,16 +3034,16 @@
         <v>38</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="K7" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="75" x14ac:dyDescent="0.25">
@@ -2958,7 +3057,7 @@
         <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>15</v>
@@ -2973,16 +3072,16 @@
         <v>43</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2996,7 +3095,7 @@
         <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>15</v>
@@ -3011,13 +3110,13 @@
         <v>48</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>49</v>
@@ -3034,7 +3133,7 @@
         <v>51</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>15</v>
@@ -3046,16 +3145,16 @@
         <v>25</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3069,7 +3168,7 @@
         <v>55</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>15</v>
@@ -3084,7 +3183,7 @@
         <v>57</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>58</v>
@@ -3101,7 +3200,7 @@
         <v>60</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>15</v>
@@ -3113,10 +3212,10 @@
         <v>25</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -3130,7 +3229,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>29</v>
@@ -3142,7 +3241,7 @@
         <v>64</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>65</v>
@@ -3159,7 +3258,7 @@
         <v>68</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>15</v>
@@ -3171,16 +3270,16 @@
         <v>38</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3194,7 +3293,7 @@
         <v>71</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>72</v>
@@ -3223,7 +3322,7 @@
         <v>78</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>29</v>
@@ -3235,21 +3334,21 @@
         <v>79</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>15</v>
@@ -3261,53 +3360,53 @@
         <v>17</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>84</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>88</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>29</v>
@@ -3316,143 +3415,143 @@
         <v>30</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>72</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>108</v>
+      <c r="C24" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>29</v>
@@ -3461,10 +3560,10 @@
         <v>30</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>65</v>
@@ -3472,10 +3571,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3492,15 +3591,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C20C51C6-6E6F-4215-9FA0-CAF40473805B}">
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33" style="2" customWidth="1"/>
+    <col min="4" max="4" width="23.85546875" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="54.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="29" style="2" customWidth="1"/>
@@ -3561,7 +3660,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>15</v>
@@ -3576,13 +3675,13 @@
         <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3596,7 +3695,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>15</v>
@@ -3611,10 +3710,10 @@
         <v>22</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3628,7 +3727,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>15</v>
@@ -3643,13 +3742,13 @@
         <v>26</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3663,7 +3762,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>29</v>
@@ -3675,10 +3774,10 @@
         <v>31</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3692,31 +3791,31 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3730,7 +3829,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>15</v>
@@ -3742,16 +3841,16 @@
         <v>38</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="K7" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="120" x14ac:dyDescent="0.25">
@@ -3765,13 +3864,13 @@
         <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
@@ -3780,16 +3879,16 @@
         <v>43</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3803,7 +3902,7 @@
         <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>15</v>
@@ -3818,13 +3917,13 @@
         <v>48</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>49</v>
@@ -3841,7 +3940,7 @@
         <v>51</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>15</v>
@@ -3853,16 +3952,16 @@
         <v>25</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3876,7 +3975,7 @@
         <v>55</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>15</v>
@@ -3891,7 +3990,7 @@
         <v>57</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>58</v>
@@ -3908,7 +4007,7 @@
         <v>60</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>15</v>
@@ -3920,10 +4019,10 @@
         <v>25</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -3937,7 +4036,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>29</v>
@@ -3949,7 +4048,7 @@
         <v>64</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>65</v>
@@ -3966,7 +4065,7 @@
         <v>68</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>15</v>
@@ -3978,16 +4077,16 @@
         <v>38</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4001,7 +4100,7 @@
         <v>71</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>72</v>
@@ -4030,7 +4129,7 @@
         <v>78</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>29</v>
@@ -4042,21 +4141,21 @@
         <v>79</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>80</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>15</v>
@@ -4068,53 +4167,53 @@
         <v>17</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>84</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>88</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>29</v>
@@ -4123,143 +4222,143 @@
         <v>30</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>72</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L23" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>108</v>
+      <c r="C24" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>29</v>
@@ -4268,10 +4367,10 @@
         <v>30</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L24" s="1" t="s">
         <v>65</v>
@@ -4279,10 +4378,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4299,15 +4398,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2BEB9BE-D1E1-427B-A8AB-8E7466BA14C6}">
   <dimension ref="A1:L24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="85.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.5703125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="21.140625" style="2" customWidth="1"/>
     <col min="5" max="5" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="54.7109375" style="1" customWidth="1"/>
     <col min="7" max="7" width="29" style="2" customWidth="1"/>
@@ -4368,7 +4467,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>15</v>
@@ -4383,13 +4482,13 @@
         <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4403,7 +4502,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>15</v>
@@ -4418,10 +4517,10 @@
         <v>22</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4435,7 +4534,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>15</v>
@@ -4450,13 +4549,13 @@
         <v>26</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4470,7 +4569,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>29</v>
@@ -4482,10 +4581,10 @@
         <v>31</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4499,31 +4598,31 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="L6" s="1" t="s">
         <v>127</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4537,7 +4636,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>15</v>
@@ -4549,16 +4648,16 @@
         <v>38</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="I7" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>132</v>
-      </c>
       <c r="K7" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="120" x14ac:dyDescent="0.25">
@@ -4572,13 +4671,13 @@
         <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
@@ -4587,13 +4686,13 @@
         <v>43</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4607,7 +4706,7 @@
         <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>15</v>
@@ -4622,16 +4721,13 @@
         <v>48</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>49</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4645,7 +4741,7 @@
         <v>51</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>15</v>
@@ -4657,16 +4753,16 @@
         <v>25</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4680,7 +4776,7 @@
         <v>55</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>15</v>
@@ -4695,10 +4791,7 @@
         <v>57</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4712,7 +4805,7 @@
         <v>60</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>15</v>
@@ -4724,10 +4817,10 @@
         <v>25</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
@@ -4741,7 +4834,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>29</v>
@@ -4753,10 +4846,7 @@
         <v>64</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="60" x14ac:dyDescent="0.25">
@@ -4770,7 +4860,7 @@
         <v>68</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>15</v>
@@ -4782,16 +4872,16 @@
         <v>38</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4805,7 +4895,7 @@
         <v>71</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>72</v>
@@ -4818,9 +4908,6 @@
       </c>
       <c r="H15" s="1" t="s">
         <v>75</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4834,7 +4921,7 @@
         <v>78</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>29</v>
@@ -4846,21 +4933,21 @@
         <v>79</v>
       </c>
       <c r="K16" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>15</v>
@@ -4872,53 +4959,53 @@
         <v>17</v>
       </c>
       <c r="H17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>29</v>
@@ -4927,143 +5014,137 @@
         <v>30</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>54</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>72</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>108</v>
+      <c r="C24" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>29</v>
@@ -5072,21 +5153,18 @@
         <v>30</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>65</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5101,4 +5179,1803 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69B6FB30-D88B-40B1-85CA-7047A25848FE}">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="29" style="2" customWidth="1"/>
+    <col min="8" max="8" width="41.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="41.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="58.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="64" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I24">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+      <formula>"KO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I24" xr:uid="{6342B8B9-39EB-4481-ABFE-C6BB42B9DEFF}">
+      <formula1>"OK,KO"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CDBE412-3DF4-4737-850E-A884982B0245}">
+  <dimension ref="A1:L24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="20.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="29" style="2" customWidth="1"/>
+    <col min="8" max="8" width="41.7109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="7.42578125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="41.7109375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="58.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="64" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="90" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="I2:I24">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"OK"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"KO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I24" xr:uid="{50A59E0D-93CC-4AB3-8241-DC68E0E3A191}">
+      <formula1>"OK,KO"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27CCBE7D-F26A-41C6-96A8-43D2BF97BCE3}">
+  <dimension ref="A1:J4"/>
+  <sheetFormatPr defaultColWidth="91.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="68.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="89.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="30.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>159</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D2:D4">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"BASSA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"MEDIA"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+      <formula>"ALTA"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D4" xr:uid="{78C482C4-A569-4755-A44B-F5FA399B9D9D}">
+      <formula1>"ALTA,MEDIA,BASSA"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/testbook/ClinicaFlow_TestBook_API.xlsx
+++ b/docs/testbook/ClinicaFlow_TestBook_API.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\valen\clinicaflow\docs\testbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D468709-F195-48D9-8F1A-5DC95484EE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{760D6AB7-D435-4D56-9168-2A44CDCC9AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-4770" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="6" xr2:uid="{1C9960E8-B103-4EFA-9509-2FD0D5F86CF0}"/>
+    <workbookView xWindow="20370" yWindow="-4770" windowWidth="29040" windowHeight="15720" xr2:uid="{1C9960E8-B103-4EFA-9509-2FD0D5F86CF0}"/>
   </bookViews>
   <sheets>
     <sheet name="ClinicaFlow_TestBook_API" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,14 @@
     <sheet name="TS3_20260321" sheetId="5" r:id="rId4"/>
     <sheet name="TS4_20260322" sheetId="6" r:id="rId5"/>
     <sheet name="TS5_20260322" sheetId="7" r:id="rId6"/>
-    <sheet name="BUG" sheetId="3" r:id="rId7"/>
+    <sheet name="BUG" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1439" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1425" uniqueCount="190">
   <si>
     <t>ID Test</t>
   </si>
@@ -175,9 +175,6 @@
     <t>Lo slot viene creato correttamente con isAvailable = true.</t>
   </si>
   <si>
-    <t>Se l'id del medico non Ã¨ 1, sostituirlo con quello reale.</t>
-  </si>
-  <si>
     <t>TC09</t>
   </si>
   <si>
@@ -202,9 +199,6 @@
     <t>L'appuntamento viene creato correttamente con stato Scheduled.</t>
   </si>
   <si>
-    <t>Usare gli id reali di paziente e slot, se diversi.</t>
-  </si>
-  <si>
     <t>TC11</t>
   </si>
   <si>
@@ -223,9 +217,6 @@
     <t>Lo slot restituito ha isAvailable = false.</t>
   </si>
   <si>
-    <t>Sostituire l'id con quello reale dello slot.</t>
-  </si>
-  <si>
     <t>TC13</t>
   </si>
   <si>
@@ -256,9 +247,6 @@
     <t>Lo stato dell'appuntamento viene aggiornato a Completed.</t>
   </si>
   <si>
-    <t>Sostituire l'id dell'appuntamento se necessario.</t>
-  </si>
-  <si>
     <t>TC15</t>
   </si>
   <si>
@@ -323,9 +311,6 @@
   </si>
   <si>
     <t>Il secondo appuntamento viene creato correttamente.</t>
-  </si>
-  <si>
-    <t>Sostituire l'id dello slot se necessario.</t>
   </si>
   <si>
     <t>TC22</t>
@@ -785,7 +770,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -967,18 +952,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor theme="4" tint="0.59999389629810485"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1094,43 +1073,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top/>
-      <bottom style="thick">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color theme="0"/>
       </left>
@@ -1143,17 +1085,6 @@
       <bottom style="thin">
         <color theme="0"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -1201,7 +1132,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1215,29 +1146,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1284,7 +1194,79 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="99">
+  <dxfs count="111">
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.59999389629810485"/>
+          <bgColor theme="4" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1656,135 +1638,154 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}" name="Table1" displayName="Table1" ref="A1:L24" totalsRowShown="0" headerRowDxfId="98" dataDxfId="97">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}" name="Table1" displayName="Table1" ref="A1:L24" totalsRowShown="0" headerRowDxfId="110" dataDxfId="109">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{3860FCCE-8AB2-4BA5-A927-55A78AF301A2}" name="ID Test" dataDxfId="96"/>
-    <tableColumn id="2" xr3:uid="{6B8298D4-C558-435B-BC50-DF9FF417402B}" name="Area" dataDxfId="95"/>
-    <tableColumn id="3" xr3:uid="{53DE22B4-8437-4EA6-813E-2F0CF7E72133}" name="Obiettivo" dataDxfId="94"/>
-    <tableColumn id="4" xr3:uid="{59024008-94B6-47E6-8C7F-69725DFAE6EC}" name="Endpoint" dataDxfId="93"/>
-    <tableColumn id="5" xr3:uid="{DC8ACE73-D608-4E52-81FB-F85282B31F51}" name="Metodo HTTP" dataDxfId="92"/>
-    <tableColumn id="6" xr3:uid="{E583E0AB-6285-4FCA-BC35-0CD0BFB6F457}" name="Payload JSON" dataDxfId="91"/>
-    <tableColumn id="7" xr3:uid="{5BDBA1B2-61ED-47D6-88D1-CDE3D8CC9212}" name="Risultato atteso - Status Code" dataDxfId="90"/>
-    <tableColumn id="8" xr3:uid="{F14E32B9-432F-43ED-9E31-411BF4ADBC3F}" name="Risultato atteso - Dettaglio" dataDxfId="89"/>
-    <tableColumn id="9" xr3:uid="{DFDF46B3-7AFF-4643-9EAB-E56F926CE154}" name="Esito" dataDxfId="88"/>
-    <tableColumn id="10" xr3:uid="{5192CEE0-B98B-4E21-8BEA-8F62C2DAC458}" name="Risultato ottenuto" dataDxfId="87"/>
-    <tableColumn id="11" xr3:uid="{E9C64C9D-7B98-4D7D-8A82-64CB9D831A1C}" name="Screenshot" dataDxfId="86"/>
-    <tableColumn id="12" xr3:uid="{D98AF63F-322C-4828-B53E-197F74FEE6FE}" name="Note" dataDxfId="85"/>
+    <tableColumn id="1" xr3:uid="{3860FCCE-8AB2-4BA5-A927-55A78AF301A2}" name="ID Test" dataDxfId="108"/>
+    <tableColumn id="2" xr3:uid="{6B8298D4-C558-435B-BC50-DF9FF417402B}" name="Area" dataDxfId="107"/>
+    <tableColumn id="3" xr3:uid="{53DE22B4-8437-4EA6-813E-2F0CF7E72133}" name="Obiettivo" dataDxfId="106"/>
+    <tableColumn id="4" xr3:uid="{59024008-94B6-47E6-8C7F-69725DFAE6EC}" name="Endpoint" dataDxfId="105"/>
+    <tableColumn id="5" xr3:uid="{DC8ACE73-D608-4E52-81FB-F85282B31F51}" name="Metodo HTTP" dataDxfId="104"/>
+    <tableColumn id="6" xr3:uid="{E583E0AB-6285-4FCA-BC35-0CD0BFB6F457}" name="Payload JSON" dataDxfId="103"/>
+    <tableColumn id="7" xr3:uid="{5BDBA1B2-61ED-47D6-88D1-CDE3D8CC9212}" name="Risultato atteso - Status Code" dataDxfId="102"/>
+    <tableColumn id="8" xr3:uid="{F14E32B9-432F-43ED-9E31-411BF4ADBC3F}" name="Risultato atteso - Dettaglio" dataDxfId="101"/>
+    <tableColumn id="9" xr3:uid="{DFDF46B3-7AFF-4643-9EAB-E56F926CE154}" name="Esito" dataDxfId="100"/>
+    <tableColumn id="10" xr3:uid="{5192CEE0-B98B-4E21-8BEA-8F62C2DAC458}" name="Risultato ottenuto" dataDxfId="99"/>
+    <tableColumn id="11" xr3:uid="{E9C64C9D-7B98-4D7D-8A82-64CB9D831A1C}" name="Screenshot" dataDxfId="98"/>
+    <tableColumn id="12" xr3:uid="{D98AF63F-322C-4828-B53E-197F74FEE6FE}" name="Note" dataDxfId="97"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5EC5406F-ABEC-4C5A-BB6C-648C616B89A5}" name="Table13" displayName="Table13" ref="A1:L24" totalsRowShown="0" headerRowDxfId="84" dataDxfId="83">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{5EC5406F-ABEC-4C5A-BB6C-648C616B89A5}" name="Table13" displayName="Table13" ref="A1:L24" totalsRowShown="0" headerRowDxfId="96" dataDxfId="95">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{5009D189-63E8-4852-A288-87D6EC1E7033}" name="ID Test" dataDxfId="82"/>
-    <tableColumn id="2" xr3:uid="{84642470-32B1-46DB-88F2-1BC4AE8F75C8}" name="Area" dataDxfId="81"/>
-    <tableColumn id="3" xr3:uid="{4F14914F-A3C4-4267-A392-EC2D02D6ADDF}" name="Obiettivo" dataDxfId="80"/>
-    <tableColumn id="4" xr3:uid="{62A87606-C1B8-47E6-9530-D288374DCDF3}" name="Endpoint" dataDxfId="79"/>
-    <tableColumn id="5" xr3:uid="{19E09EE6-EB67-45CF-9A03-E0F0523DB6A0}" name="Metodo HTTP" dataDxfId="78"/>
-    <tableColumn id="6" xr3:uid="{A7AC84FA-A2F1-4930-BDDD-E380EE204368}" name="Payload JSON" dataDxfId="77"/>
-    <tableColumn id="7" xr3:uid="{25C18B10-E594-4E87-AD84-2A557086D8F7}" name="Risultato atteso - Status Code" dataDxfId="76"/>
-    <tableColumn id="8" xr3:uid="{94B79096-6200-43FE-8F50-1C48EB575740}" name="Risultato atteso - Dettaglio" dataDxfId="75"/>
-    <tableColumn id="9" xr3:uid="{AD4E1447-793D-4E65-9313-6A19D961F6AE}" name="Esito" dataDxfId="74"/>
-    <tableColumn id="10" xr3:uid="{B18252F9-BB1D-47B7-8E2C-F42387EC3664}" name="Risultato ottenuto" dataDxfId="73"/>
-    <tableColumn id="11" xr3:uid="{15A8AB07-0563-4A1C-839B-92039F98E2D5}" name="Screenshot" dataDxfId="72"/>
-    <tableColumn id="12" xr3:uid="{4BA21C77-65A7-407A-A5E1-0AA6154386E8}" name="Note" dataDxfId="71"/>
+    <tableColumn id="1" xr3:uid="{5009D189-63E8-4852-A288-87D6EC1E7033}" name="ID Test" dataDxfId="94"/>
+    <tableColumn id="2" xr3:uid="{84642470-32B1-46DB-88F2-1BC4AE8F75C8}" name="Area" dataDxfId="93"/>
+    <tableColumn id="3" xr3:uid="{4F14914F-A3C4-4267-A392-EC2D02D6ADDF}" name="Obiettivo" dataDxfId="92"/>
+    <tableColumn id="4" xr3:uid="{62A87606-C1B8-47E6-9530-D288374DCDF3}" name="Endpoint" dataDxfId="91"/>
+    <tableColumn id="5" xr3:uid="{19E09EE6-EB67-45CF-9A03-E0F0523DB6A0}" name="Metodo HTTP" dataDxfId="90"/>
+    <tableColumn id="6" xr3:uid="{A7AC84FA-A2F1-4930-BDDD-E380EE204368}" name="Payload JSON" dataDxfId="89"/>
+    <tableColumn id="7" xr3:uid="{25C18B10-E594-4E87-AD84-2A557086D8F7}" name="Risultato atteso - Status Code" dataDxfId="88"/>
+    <tableColumn id="8" xr3:uid="{94B79096-6200-43FE-8F50-1C48EB575740}" name="Risultato atteso - Dettaglio" dataDxfId="87"/>
+    <tableColumn id="9" xr3:uid="{AD4E1447-793D-4E65-9313-6A19D961F6AE}" name="Esito" dataDxfId="86"/>
+    <tableColumn id="10" xr3:uid="{B18252F9-BB1D-47B7-8E2C-F42387EC3664}" name="Risultato ottenuto" dataDxfId="85"/>
+    <tableColumn id="11" xr3:uid="{15A8AB07-0563-4A1C-839B-92039F98E2D5}" name="Screenshot" dataDxfId="84"/>
+    <tableColumn id="12" xr3:uid="{4BA21C77-65A7-407A-A5E1-0AA6154386E8}" name="Note" dataDxfId="83"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3C84183B-2219-4217-B03E-3888C2A1762E}" name="Table134" displayName="Table134" ref="A1:L24" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{3C84183B-2219-4217-B03E-3888C2A1762E}" name="Table134" displayName="Table134" ref="A1:L24" totalsRowShown="0" headerRowDxfId="82" dataDxfId="81">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{B704E338-5C37-41FB-8C85-99D253E12A36}" name="ID Test" dataDxfId="68"/>
-    <tableColumn id="2" xr3:uid="{B2981A3F-A838-4564-95CD-018029141FE3}" name="Area" dataDxfId="67"/>
-    <tableColumn id="3" xr3:uid="{3A09ED62-C911-40F8-84B2-95FDC9F0E73C}" name="Obiettivo" dataDxfId="66"/>
-    <tableColumn id="4" xr3:uid="{7D97DC0F-3E73-4208-8A63-D6DE3FC761AA}" name="Endpoint" dataDxfId="65"/>
-    <tableColumn id="5" xr3:uid="{FF0C5D75-36E7-48D4-A80F-888A5CC255B7}" name="Metodo HTTP" dataDxfId="64"/>
-    <tableColumn id="6" xr3:uid="{023149CE-2E87-48C5-89F0-C06C9BB739DA}" name="Payload JSON" dataDxfId="63"/>
-    <tableColumn id="7" xr3:uid="{8BAEE933-7939-4263-9D14-00FEC91A9C1B}" name="Risultato atteso - Status Code" dataDxfId="62"/>
-    <tableColumn id="8" xr3:uid="{8D31C62B-63D8-4839-9FA3-50CF6221E2BA}" name="Risultato atteso - Dettaglio" dataDxfId="61"/>
-    <tableColumn id="9" xr3:uid="{718B97BF-78C2-4F95-B210-9079004CD606}" name="Esito" dataDxfId="60"/>
-    <tableColumn id="10" xr3:uid="{5CFD81E3-BB64-412E-85AA-84B4611A7F83}" name="Risultato ottenuto" dataDxfId="59"/>
-    <tableColumn id="11" xr3:uid="{6A9BDE4A-CBAC-4363-A060-8EA060236295}" name="Screenshot" dataDxfId="58"/>
-    <tableColumn id="12" xr3:uid="{4E358191-7A4E-4452-AC66-1FBA8A472BD5}" name="Note" dataDxfId="57"/>
+    <tableColumn id="1" xr3:uid="{B704E338-5C37-41FB-8C85-99D253E12A36}" name="ID Test" dataDxfId="80"/>
+    <tableColumn id="2" xr3:uid="{B2981A3F-A838-4564-95CD-018029141FE3}" name="Area" dataDxfId="79"/>
+    <tableColumn id="3" xr3:uid="{3A09ED62-C911-40F8-84B2-95FDC9F0E73C}" name="Obiettivo" dataDxfId="78"/>
+    <tableColumn id="4" xr3:uid="{7D97DC0F-3E73-4208-8A63-D6DE3FC761AA}" name="Endpoint" dataDxfId="77"/>
+    <tableColumn id="5" xr3:uid="{FF0C5D75-36E7-48D4-A80F-888A5CC255B7}" name="Metodo HTTP" dataDxfId="76"/>
+    <tableColumn id="6" xr3:uid="{023149CE-2E87-48C5-89F0-C06C9BB739DA}" name="Payload JSON" dataDxfId="75"/>
+    <tableColumn id="7" xr3:uid="{8BAEE933-7939-4263-9D14-00FEC91A9C1B}" name="Risultato atteso - Status Code" dataDxfId="74"/>
+    <tableColumn id="8" xr3:uid="{8D31C62B-63D8-4839-9FA3-50CF6221E2BA}" name="Risultato atteso - Dettaglio" dataDxfId="73"/>
+    <tableColumn id="9" xr3:uid="{718B97BF-78C2-4F95-B210-9079004CD606}" name="Esito" dataDxfId="72"/>
+    <tableColumn id="10" xr3:uid="{5CFD81E3-BB64-412E-85AA-84B4611A7F83}" name="Risultato ottenuto" dataDxfId="71"/>
+    <tableColumn id="11" xr3:uid="{6A9BDE4A-CBAC-4363-A060-8EA060236295}" name="Screenshot" dataDxfId="70"/>
+    <tableColumn id="12" xr3:uid="{4E358191-7A4E-4452-AC66-1FBA8A472BD5}" name="Note" dataDxfId="69"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5392533B-6B0E-4F8C-A890-54E0F381453F}" name="Table1345" displayName="Table1345" ref="A1:L24" totalsRowShown="0" headerRowDxfId="56" dataDxfId="55">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5392533B-6B0E-4F8C-A890-54E0F381453F}" name="Table1345" displayName="Table1345" ref="A1:L24" totalsRowShown="0" headerRowDxfId="68" dataDxfId="67">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{5DB9B359-E545-4837-92D9-C3F683AC6170}" name="ID Test" dataDxfId="54"/>
-    <tableColumn id="2" xr3:uid="{3357AA3D-D573-45C9-9E54-169DE6BCCC7B}" name="Area" dataDxfId="53"/>
-    <tableColumn id="3" xr3:uid="{FE4BC87A-DD7A-4AC5-9DF0-39C04CF1DEDC}" name="Obiettivo" dataDxfId="52"/>
-    <tableColumn id="4" xr3:uid="{61F99A4D-AC1D-4AAE-BD37-39FC313ECF7E}" name="Endpoint" dataDxfId="51"/>
-    <tableColumn id="5" xr3:uid="{5FD12983-51FF-4BBD-B2DE-46FBD352051D}" name="Metodo HTTP" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{B67C064B-9915-4F2D-8311-0F58E542AA8C}" name="Payload JSON" dataDxfId="49"/>
-    <tableColumn id="7" xr3:uid="{8875AB99-AAA8-46E7-8416-18C1D1E6E0D6}" name="Risultato atteso - Status Code" dataDxfId="48"/>
-    <tableColumn id="8" xr3:uid="{6DA0A166-C4F1-4D89-874B-4007FF063015}" name="Risultato atteso - Dettaglio" dataDxfId="47"/>
-    <tableColumn id="9" xr3:uid="{C4E9099C-524E-4645-AE6E-B8ACEAF227A2}" name="Esito" dataDxfId="46"/>
-    <tableColumn id="10" xr3:uid="{8329D30F-DF3B-4467-8F69-F9BE9E265DCA}" name="Risultato ottenuto" dataDxfId="45"/>
-    <tableColumn id="11" xr3:uid="{99A837AC-AC32-4D7E-BCA2-CEC29E347BE5}" name="Screenshot" dataDxfId="44"/>
-    <tableColumn id="12" xr3:uid="{05FA14BC-760C-4AFA-975E-E185779DFF89}" name="Note" dataDxfId="43"/>
+    <tableColumn id="1" xr3:uid="{5DB9B359-E545-4837-92D9-C3F683AC6170}" name="ID Test" dataDxfId="66"/>
+    <tableColumn id="2" xr3:uid="{3357AA3D-D573-45C9-9E54-169DE6BCCC7B}" name="Area" dataDxfId="65"/>
+    <tableColumn id="3" xr3:uid="{FE4BC87A-DD7A-4AC5-9DF0-39C04CF1DEDC}" name="Obiettivo" dataDxfId="64"/>
+    <tableColumn id="4" xr3:uid="{61F99A4D-AC1D-4AAE-BD37-39FC313ECF7E}" name="Endpoint" dataDxfId="63"/>
+    <tableColumn id="5" xr3:uid="{5FD12983-51FF-4BBD-B2DE-46FBD352051D}" name="Metodo HTTP" dataDxfId="62"/>
+    <tableColumn id="6" xr3:uid="{B67C064B-9915-4F2D-8311-0F58E542AA8C}" name="Payload JSON" dataDxfId="61"/>
+    <tableColumn id="7" xr3:uid="{8875AB99-AAA8-46E7-8416-18C1D1E6E0D6}" name="Risultato atteso - Status Code" dataDxfId="60"/>
+    <tableColumn id="8" xr3:uid="{6DA0A166-C4F1-4D89-874B-4007FF063015}" name="Risultato atteso - Dettaglio" dataDxfId="59"/>
+    <tableColumn id="9" xr3:uid="{C4E9099C-524E-4645-AE6E-B8ACEAF227A2}" name="Esito" dataDxfId="58"/>
+    <tableColumn id="10" xr3:uid="{8329D30F-DF3B-4467-8F69-F9BE9E265DCA}" name="Risultato ottenuto" dataDxfId="57"/>
+    <tableColumn id="11" xr3:uid="{99A837AC-AC32-4D7E-BCA2-CEC29E347BE5}" name="Screenshot" dataDxfId="56"/>
+    <tableColumn id="12" xr3:uid="{05FA14BC-760C-4AFA-975E-E185779DFF89}" name="Note" dataDxfId="55"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{28F10800-5F17-4DF4-A265-9540A82D8F49}" name="Table13456" displayName="Table13456" ref="A1:L24" totalsRowShown="0" headerRowDxfId="42" dataDxfId="41">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{28F10800-5F17-4DF4-A265-9540A82D8F49}" name="Table13456" displayName="Table13456" ref="A1:L24" totalsRowShown="0" headerRowDxfId="54" dataDxfId="53">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{63214038-0043-4A32-AF2E-81FCC7E0E959}" name="ID Test" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{DA94D99B-D0CD-4C28-90D5-7D36DEEDED54}" name="Area" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{860DD01C-3A8E-48EE-9E95-D5ED1A4B8AF3}" name="Obiettivo" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{C311DD5F-6C88-4F21-9480-8419A1D24693}" name="Endpoint" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{AFCD354B-2A4F-412F-8FF0-4E34F43379DC}" name="Metodo HTTP" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{666265C9-EBE4-4901-944B-B821A3D713C8}" name="Payload JSON" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{7AD7F2D9-9A10-474B-A4BA-BF7F2688D184}" name="Risultato atteso - Status Code" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{53F65EF7-BF0C-48A0-BB4B-34BF9E2D6AB7}" name="Risultato atteso - Dettaglio" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{586EA1BD-3E26-4E9F-8B58-99210DFA6D75}" name="Esito" dataDxfId="32"/>
-    <tableColumn id="10" xr3:uid="{FC30B956-A42E-4863-B26D-CD1CE586B61C}" name="Risultato ottenuto" dataDxfId="31"/>
-    <tableColumn id="11" xr3:uid="{38D8A589-74FA-48A3-B607-721851799674}" name="Screenshot" dataDxfId="30"/>
-    <tableColumn id="12" xr3:uid="{2555A3BC-E4BE-4790-A872-4E791D4BE524}" name="Note" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{63214038-0043-4A32-AF2E-81FCC7E0E959}" name="ID Test" dataDxfId="52"/>
+    <tableColumn id="2" xr3:uid="{DA94D99B-D0CD-4C28-90D5-7D36DEEDED54}" name="Area" dataDxfId="51"/>
+    <tableColumn id="3" xr3:uid="{860DD01C-3A8E-48EE-9E95-D5ED1A4B8AF3}" name="Obiettivo" dataDxfId="50"/>
+    <tableColumn id="4" xr3:uid="{C311DD5F-6C88-4F21-9480-8419A1D24693}" name="Endpoint" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{AFCD354B-2A4F-412F-8FF0-4E34F43379DC}" name="Metodo HTTP" dataDxfId="48"/>
+    <tableColumn id="6" xr3:uid="{666265C9-EBE4-4901-944B-B821A3D713C8}" name="Payload JSON" dataDxfId="47"/>
+    <tableColumn id="7" xr3:uid="{7AD7F2D9-9A10-474B-A4BA-BF7F2688D184}" name="Risultato atteso - Status Code" dataDxfId="46"/>
+    <tableColumn id="8" xr3:uid="{53F65EF7-BF0C-48A0-BB4B-34BF9E2D6AB7}" name="Risultato atteso - Dettaglio" dataDxfId="45"/>
+    <tableColumn id="9" xr3:uid="{586EA1BD-3E26-4E9F-8B58-99210DFA6D75}" name="Esito" dataDxfId="44"/>
+    <tableColumn id="10" xr3:uid="{FC30B956-A42E-4863-B26D-CD1CE586B61C}" name="Risultato ottenuto" dataDxfId="43"/>
+    <tableColumn id="11" xr3:uid="{38D8A589-74FA-48A3-B607-721851799674}" name="Screenshot" dataDxfId="42"/>
+    <tableColumn id="12" xr3:uid="{2555A3BC-E4BE-4790-A872-4E791D4BE524}" name="Note" dataDxfId="41"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{42FC6E2F-12D2-4B07-83FE-5568C141ED11}" name="Table134567" displayName="Table134567" ref="A1:L24" totalsRowShown="0" headerRowDxfId="28" dataDxfId="27">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{42FC6E2F-12D2-4B07-83FE-5568C141ED11}" name="Table134567" displayName="Table134567" ref="A1:L24" totalsRowShown="0" headerRowDxfId="40" dataDxfId="39">
   <autoFilter ref="A1:L24" xr:uid="{5E234CF2-B3FB-42E4-9C2F-2101E3219E96}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{4C6B92BD-7AE4-4837-9A54-CCAFFF439227}" name="ID Test" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{46BBB285-C581-46F6-8FD2-761048895C44}" name="Area" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{DAC70DE0-1731-4FF2-904B-BE773769384C}" name="Obiettivo" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{DEB47A3E-0270-48FB-98B6-8A232FDFCFCE}" name="Endpoint" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{71FF2070-0AD2-4FC5-ACAE-A7B00B48E2A7}" name="Metodo HTTP" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{DFAEB569-EFF2-48F3-9456-5279864957F5}" name="Payload JSON" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{CE89C81C-1169-4A34-873C-ED12BB2E88FD}" name="Risultato atteso - Status Code" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{83059EF0-2287-4D73-949B-360391CB89F9}" name="Risultato atteso - Dettaglio" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{EA9E5C2E-4549-44C4-9E4A-438269678451}" name="Esito" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{4979933D-EB34-41F5-8643-936F826A3AF4}" name="Risultato ottenuto" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{22F04AFA-26CC-44FD-9673-D56BEC383839}" name="Screenshot" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{29D1856A-E944-4770-AB5F-BF2439CEDF3E}" name="Note" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{4C6B92BD-7AE4-4837-9A54-CCAFFF439227}" name="ID Test" dataDxfId="38"/>
+    <tableColumn id="2" xr3:uid="{46BBB285-C581-46F6-8FD2-761048895C44}" name="Area" dataDxfId="37"/>
+    <tableColumn id="3" xr3:uid="{DAC70DE0-1731-4FF2-904B-BE773769384C}" name="Obiettivo" dataDxfId="36"/>
+    <tableColumn id="4" xr3:uid="{DEB47A3E-0270-48FB-98B6-8A232FDFCFCE}" name="Endpoint" dataDxfId="35"/>
+    <tableColumn id="5" xr3:uid="{71FF2070-0AD2-4FC5-ACAE-A7B00B48E2A7}" name="Metodo HTTP" dataDxfId="34"/>
+    <tableColumn id="6" xr3:uid="{DFAEB569-EFF2-48F3-9456-5279864957F5}" name="Payload JSON" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{CE89C81C-1169-4A34-873C-ED12BB2E88FD}" name="Risultato atteso - Status Code" dataDxfId="32"/>
+    <tableColumn id="8" xr3:uid="{83059EF0-2287-4D73-949B-360391CB89F9}" name="Risultato atteso - Dettaglio" dataDxfId="31"/>
+    <tableColumn id="9" xr3:uid="{EA9E5C2E-4549-44C4-9E4A-438269678451}" name="Esito" dataDxfId="30"/>
+    <tableColumn id="10" xr3:uid="{4979933D-EB34-41F5-8643-936F826A3AF4}" name="Risultato ottenuto" dataDxfId="29"/>
+    <tableColumn id="11" xr3:uid="{22F04AFA-26CC-44FD-9673-D56BEC383839}" name="Screenshot" dataDxfId="28"/>
+    <tableColumn id="12" xr3:uid="{29D1856A-E944-4770-AB5F-BF2439CEDF3E}" name="Note" dataDxfId="27"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{BEFA339F-C58C-4E8E-A187-14513C5806AE}" name="Table9" displayName="Table9" ref="A1:J4" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+  <autoFilter ref="A1:J4" xr:uid="{BEFA339F-C58C-4E8E-A187-14513C5806AE}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{4EFF7D36-00ED-4F09-BDAE-73A9ED4C233A}" name="ID Bug" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{F8BECB35-6ED8-4ED0-A5B2-FF273B9367B0}" name="ID Test" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{535E5EA6-C580-4404-BA47-0575FE5CD60E}" name="Area" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{7DD7FCC2-1292-402A-BCAF-31F80BB76256}" name="Priorità" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{EE6AE75E-BCC7-41A7-B5B4-574297C708E3}" name="Sessione KO" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{8330ADB1-9A41-4202-B882-BBE4E1E56F8D}" name="Sessione OK" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{EE2B4D2B-0663-4155-B6BB-6472780FC0AD}" name="Endpoint" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{01380020-6D3B-4B98-8660-E4E321B86928}" name="Metodo HTTP" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{4F42B234-4B78-43CA-97DD-AA35E5EBB694}" name="Payload JSON" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{1007C6AC-F2A9-4B21-9E31-7DD1134E9A29}" name="Errore" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium14" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1822,7 +1823,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1928,7 +1929,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2070,7 +2071,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2145,7 +2146,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>15</v>
@@ -2160,7 +2161,7 @@
         <v>18</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2174,7 +2175,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>15</v>
@@ -2200,7 +2201,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>15</v>
@@ -2215,7 +2216,7 @@
         <v>26</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2229,7 +2230,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>29</v>
@@ -2252,22 +2253,22 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2281,7 +2282,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>15</v>
@@ -2293,10 +2294,10 @@
         <v>38</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="60" x14ac:dyDescent="0.25">
@@ -2310,7 +2311,7 @@
         <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>15</v>
@@ -2325,7 +2326,7 @@
         <v>43</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2339,7 +2340,7 @@
         <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>15</v>
@@ -2354,108 +2355,108 @@
         <v>48</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>29</v>
@@ -2464,79 +2465,79 @@
         <v>30</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="H15" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>29</v>
@@ -2545,82 +2546,82 @@
         <v>30</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>29</v>
@@ -2629,125 +2630,125 @@
         <v>30</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>29</v>
@@ -2756,22 +2757,22 @@
         <v>30</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I2:I24" xr:uid="{1E5ABA8E-0832-445D-8BB0-BB6759FFFC93}">
       <formula1>"OK,KO"</formula1>
     </dataValidation>
@@ -2853,7 +2854,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>15</v>
@@ -2868,13 +2869,13 @@
         <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2888,7 +2889,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>15</v>
@@ -2903,10 +2904,10 @@
         <v>22</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2920,7 +2921,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>15</v>
@@ -2935,13 +2936,13 @@
         <v>26</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2955,7 +2956,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>29</v>
@@ -2967,10 +2968,10 @@
         <v>31</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -2984,31 +2985,31 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3022,7 +3023,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>15</v>
@@ -3034,16 +3035,16 @@
         <v>38</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="75" x14ac:dyDescent="0.25">
@@ -3057,7 +3058,7 @@
         <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>15</v>
@@ -3072,16 +3073,16 @@
         <v>43</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3095,7 +3096,7 @@
         <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>15</v>
@@ -3110,126 +3111,120 @@
         <v>48</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>29</v>
@@ -3238,91 +3233,85 @@
         <v>30</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="H15" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>29</v>
@@ -3331,82 +3320,82 @@
         <v>30</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>29</v>
@@ -3415,143 +3404,137 @@
         <v>30</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="L22" s="1" t="s">
+    </row>
+    <row r="24" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="75" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>29</v>
@@ -3560,21 +3543,18 @@
         <v>30</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>65</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3660,7 +3640,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>15</v>
@@ -3675,13 +3655,13 @@
         <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3695,7 +3675,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>15</v>
@@ -3710,10 +3690,10 @@
         <v>22</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3727,7 +3707,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>15</v>
@@ -3742,13 +3722,13 @@
         <v>26</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3762,7 +3742,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>29</v>
@@ -3774,10 +3754,10 @@
         <v>31</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3791,31 +3771,31 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3829,7 +3809,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>15</v>
@@ -3841,16 +3821,16 @@
         <v>38</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="120" x14ac:dyDescent="0.25">
@@ -3864,13 +3844,13 @@
         <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
@@ -3879,16 +3859,16 @@
         <v>43</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -3902,7 +3882,7 @@
         <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>15</v>
@@ -3917,126 +3897,120 @@
         <v>48</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>58</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>29</v>
@@ -4045,91 +4019,85 @@
         <v>30</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>65</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="H15" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>29</v>
@@ -4138,82 +4106,82 @@
         <v>30</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="60" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>29</v>
@@ -4222,143 +4190,137 @@
         <v>30</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="L22" s="1" t="s">
+    </row>
+    <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="60" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>29</v>
@@ -4367,21 +4329,18 @@
         <v>30</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>65</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4467,7 +4426,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>15</v>
@@ -4482,13 +4441,13 @@
         <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4502,7 +4461,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>15</v>
@@ -4517,10 +4476,10 @@
         <v>22</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4534,7 +4493,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>15</v>
@@ -4549,13 +4508,13 @@
         <v>26</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4569,7 +4528,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>29</v>
@@ -4581,10 +4540,10 @@
         <v>31</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4598,31 +4557,31 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4636,7 +4595,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>15</v>
@@ -4648,16 +4607,16 @@
         <v>38</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="120" x14ac:dyDescent="0.25">
@@ -4671,13 +4630,13 @@
         <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
@@ -4686,13 +4645,13 @@
         <v>43</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
@@ -4706,7 +4665,7 @@
         <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>15</v>
@@ -4721,120 +4680,120 @@
         <v>48</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>56</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>29</v>
@@ -4843,85 +4802,85 @@
         <v>30</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="H15" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>29</v>
@@ -4930,82 +4889,82 @@
         <v>30</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>29</v>
@@ -5014,137 +4973,137 @@
         <v>30</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>29</v>
@@ -5153,18 +5112,18 @@
         <v>30</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5250,7 +5209,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>15</v>
@@ -5265,13 +5224,13 @@
         <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="75" x14ac:dyDescent="0.25">
@@ -5285,7 +5244,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>15</v>
@@ -5300,10 +5259,10 @@
         <v>22</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="75" x14ac:dyDescent="0.25">
@@ -5317,7 +5276,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>15</v>
@@ -5332,13 +5291,13 @@
         <v>26</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="60" x14ac:dyDescent="0.25">
@@ -5352,7 +5311,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>29</v>
@@ -5364,10 +5323,10 @@
         <v>31</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="75" x14ac:dyDescent="0.25">
@@ -5381,31 +5340,31 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="90" x14ac:dyDescent="0.25">
@@ -5419,7 +5378,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>15</v>
@@ -5431,16 +5390,16 @@
         <v>38</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="120" x14ac:dyDescent="0.25">
@@ -5454,13 +5413,13 @@
         <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
@@ -5469,13 +5428,13 @@
         <v>43</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="45" x14ac:dyDescent="0.25">
@@ -5489,7 +5448,7 @@
         <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>15</v>
@@ -5504,126 +5463,126 @@
         <v>48</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>59</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>29</v>
@@ -5632,85 +5591,85 @@
         <v>30</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="G15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="H15" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>29</v>
@@ -5719,82 +5678,82 @@
         <v>30</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>29</v>
@@ -5803,137 +5762,137 @@
         <v>30</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>29</v>
@@ -5942,18 +5901,18 @@
         <v>30</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="6" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6039,7 +5998,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>15</v>
@@ -6054,13 +6013,13 @@
         <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="75" x14ac:dyDescent="0.25">
@@ -6074,7 +6033,7 @@
         <v>20</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>15</v>
@@ -6089,10 +6048,10 @@
         <v>22</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="75" x14ac:dyDescent="0.25">
@@ -6106,7 +6065,7 @@
         <v>24</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>15</v>
@@ -6121,13 +6080,13 @@
         <v>26</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="60" x14ac:dyDescent="0.25">
@@ -6141,7 +6100,7 @@
         <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>29</v>
@@ -6153,10 +6112,10 @@
         <v>31</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="75" x14ac:dyDescent="0.25">
@@ -6170,31 +6129,31 @@
         <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="90" x14ac:dyDescent="0.25">
@@ -6208,7 +6167,7 @@
         <v>36</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>15</v>
@@ -6220,16 +6179,16 @@
         <v>38</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J7" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="120" x14ac:dyDescent="0.25">
@@ -6243,13 +6202,13 @@
         <v>41</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>17</v>
@@ -6258,13 +6217,13 @@
         <v>43</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="45" x14ac:dyDescent="0.25">
@@ -6278,7 +6237,7 @@
         <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>15</v>
@@ -6293,135 +6252,135 @@
         <v>48</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>51</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="D11" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>29</v>
@@ -6430,97 +6389,97 @@
         <v>30</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>38</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="G15" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="H15" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F15" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="I15" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>29</v>
@@ -6529,97 +6488,97 @@
         <v>30</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>29</v>
@@ -6628,152 +6587,152 @@
         <v>30</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>25</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="75" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>17</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>45</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>29</v>
@@ -6782,21 +6741,21 @@
         <v>30</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I2:I24">
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"OK"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="2" operator="equal">
       <formula>"KO"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6814,168 +6773,170 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27CCBE7D-F26A-41C6-96A8-43D2BF97BCE3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D025631A-7F49-4C30-B8FA-6787BEA9218C}">
   <dimension ref="A1:J4"/>
-  <sheetFormatPr defaultColWidth="91.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="68.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="89.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38" style="1" customWidth="1"/>
+    <col min="10" max="10" width="37.28515625" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="B1" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="11" t="s">
+      <c r="G1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="120" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="11" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="30.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="12" t="s">
+      <c r="J3" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="F2" s="8" t="s">
+    </row>
+    <row r="4" spans="1:10" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="120" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>172</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>171</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="D2:D4">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"BASSA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="2" operator="equal">
       <formula>"MEDIA"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="3" operator="equal">
       <formula>"ALTA"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D4" xr:uid="{78C482C4-A569-4755-A44B-F5FA399B9D9D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D4" xr:uid="{E181C95C-AFF6-4D93-9E4D-4D386594F36C}">
       <formula1>"ALTA,MEDIA,BASSA"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>